--- a/research/traditional_assets/database/data/france/france_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/france/france_coal_related_energy.xlsx
@@ -1376,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1513,13 +1513,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.2074511430592712</v>
+      </c>
+      <c r="C2">
+        <v>2.685533962548894</v>
+      </c>
+      <c r="D2">
+        <v>2.765933962548894</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.0804</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0804</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1540,43 +1549,45 @@
         <v>-2.71</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01895832</v>
       </c>
       <c r="N2">
-        <v>-2.71</v>
+        <v>-2.728958319999999</v>
       </c>
       <c r="O2">
-        <v>-0.6774999999999999</v>
+        <v>-0.6822395799999998</v>
       </c>
       <c r="P2">
-        <v>-2.0325</v>
+        <v>-2.046718739999999</v>
       </c>
       <c r="Q2">
-        <v>3.6475</v>
+        <v>3.63328126</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.1220474483889317</v>
+      </c>
+      <c r="T2">
+        <v>1.486204688401333</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2358</v>
+      </c>
+      <c r="V2">
+        <v>-35.73628886947788</v>
+      </c>
+      <c r="W2">
+        <v>8.662416915422885</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-142.9451554779115</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1584,22 +1595,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2074511430592712</v>
+        <v>0.2093511430592712</v>
       </c>
       <c r="C3">
-        <v>2.685533962548894</v>
+        <v>2.57300166172518</v>
       </c>
       <c r="D3">
-        <v>2.765933962548894</v>
+        <v>2.73380166172518</v>
       </c>
       <c r="E3">
-        <v>0.0804</v>
+        <v>0.1608</v>
       </c>
       <c r="F3">
-        <v>0.0804</v>
+        <v>0.1608</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1620,37 +1631,37 @@
         <v>-2.71</v>
       </c>
       <c r="M3">
-        <v>0.01895832</v>
+        <v>0.03791664</v>
       </c>
       <c r="N3">
-        <v>-2.728958319999999</v>
+        <v>-2.74791664</v>
       </c>
       <c r="O3">
-        <v>-0.6822395799999998</v>
+        <v>-0.6869791599999999</v>
       </c>
       <c r="P3">
-        <v>-2.046718739999999</v>
+        <v>-2.06093748</v>
       </c>
       <c r="Q3">
-        <v>3.63328126</v>
+        <v>3.61906252</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1220474483889317</v>
+        <v>0.1228254835765738</v>
       </c>
       <c r="T3">
-        <v>1.486204688401333</v>
+        <v>1.501370042364612</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-35.73628886947788</v>
+        <v>-17.86814443473894</v>
       </c>
       <c r="W3">
-        <v>8.662416915422885</v>
+        <v>4.449108457711443</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1658,7 +1669,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-142.9451554779115</v>
+        <v>-71.47257773895576</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1666,22 +1677,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2093511430592712</v>
+        <v>0.2112511430592712</v>
       </c>
       <c r="C4">
-        <v>2.57300166172518</v>
+        <v>2.461207359689944</v>
       </c>
       <c r="D4">
-        <v>2.73380166172518</v>
+        <v>2.702407359689944</v>
       </c>
       <c r="E4">
-        <v>0.1608</v>
+        <v>0.2412</v>
       </c>
       <c r="F4">
-        <v>0.1608</v>
+        <v>0.2412</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1702,37 +1713,37 @@
         <v>-2.71</v>
       </c>
       <c r="M4">
-        <v>0.03791664</v>
+        <v>0.05687496</v>
       </c>
       <c r="N4">
-        <v>-2.74791664</v>
+        <v>-2.76687496</v>
       </c>
       <c r="O4">
-        <v>-0.6869791599999999</v>
+        <v>-0.6917187399999999</v>
       </c>
       <c r="P4">
-        <v>-2.06093748</v>
+        <v>-2.07515622</v>
       </c>
       <c r="Q4">
-        <v>3.61906252</v>
+        <v>3.60484378</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1228254835765738</v>
+        <v>0.1236195607268478</v>
       </c>
       <c r="T4">
-        <v>1.501370042364612</v>
+        <v>1.516848084038474</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-17.86814443473894</v>
+        <v>-11.91209628982596</v>
       </c>
       <c r="W4">
-        <v>4.449108457711443</v>
+        <v>3.044672305140962</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1740,7 +1751,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-71.47257773895576</v>
+        <v>-47.64838515930384</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1748,22 +1759,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2112511430592712</v>
+        <v>0.2131511430592712</v>
       </c>
       <c r="C5">
-        <v>2.461207359689944</v>
+        <v>2.350125920115956</v>
       </c>
       <c r="D5">
-        <v>2.702407359689944</v>
+        <v>2.671725920115956</v>
       </c>
       <c r="E5">
-        <v>0.2412</v>
+        <v>0.3216</v>
       </c>
       <c r="F5">
-        <v>0.2412</v>
+        <v>0.3216</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1784,37 +1795,37 @@
         <v>-2.71</v>
       </c>
       <c r="M5">
-        <v>0.05687496</v>
+        <v>0.07583328</v>
       </c>
       <c r="N5">
-        <v>-2.76687496</v>
+        <v>-2.785833279999999</v>
       </c>
       <c r="O5">
-        <v>-0.6917187399999999</v>
+        <v>-0.6964583199999999</v>
       </c>
       <c r="P5">
-        <v>-2.07515622</v>
+        <v>-2.08937496</v>
       </c>
       <c r="Q5">
-        <v>3.60484378</v>
+        <v>3.59062504</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1236195607268478</v>
+        <v>0.1244301811510858</v>
       </c>
       <c r="T5">
-        <v>1.516848084038474</v>
+        <v>1.532648584913875</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-11.91209628982596</v>
+        <v>-8.93407221736947</v>
       </c>
       <c r="W5">
-        <v>3.044672305140962</v>
+        <v>2.342454228855721</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1822,7 +1833,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-47.64838515930384</v>
+        <v>-35.73628886947787</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1830,22 +1841,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2131511430592712</v>
+        <v>0.2150511430592712</v>
       </c>
       <c r="C6">
-        <v>2.350125920115956</v>
+        <v>2.239733335389702</v>
       </c>
       <c r="D6">
-        <v>2.671725920115956</v>
+        <v>2.641733335389703</v>
       </c>
       <c r="E6">
-        <v>0.3216</v>
+        <v>0.402</v>
       </c>
       <c r="F6">
-        <v>0.3216</v>
+        <v>0.402</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1866,37 +1877,37 @@
         <v>-2.71</v>
       </c>
       <c r="M6">
-        <v>0.07583328</v>
+        <v>0.09479159999999999</v>
       </c>
       <c r="N6">
-        <v>-2.785833279999999</v>
+        <v>-2.8047916</v>
       </c>
       <c r="O6">
-        <v>-0.6964583199999999</v>
+        <v>-0.7011978999999999</v>
       </c>
       <c r="P6">
-        <v>-2.08937496</v>
+        <v>-2.1035937</v>
       </c>
       <c r="Q6">
-        <v>3.59062504</v>
+        <v>3.5764063</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1244301811510858</v>
+        <v>0.1252578672684656</v>
       </c>
       <c r="T6">
-        <v>1.532648584913875</v>
+        <v>1.548781727912968</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-8.93407221736947</v>
+        <v>-7.147257773895577</v>
       </c>
       <c r="W6">
-        <v>2.342454228855721</v>
+        <v>1.921123383084577</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1904,7 +1915,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-35.73628886947787</v>
+        <v>-28.58903109558231</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1912,22 +1923,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2150511430592712</v>
+        <v>0.2169511430592712</v>
       </c>
       <c r="C7">
-        <v>2.239733335389702</v>
+        <v>2.130006663960449</v>
       </c>
       <c r="D7">
-        <v>2.641733335389703</v>
+        <v>2.612406663960449</v>
       </c>
       <c r="E7">
-        <v>0.402</v>
+        <v>0.4824</v>
       </c>
       <c r="F7">
-        <v>0.402</v>
+        <v>0.4824</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1948,37 +1959,37 @@
         <v>-2.71</v>
       </c>
       <c r="M7">
-        <v>0.09479159999999999</v>
+        <v>0.11374992</v>
       </c>
       <c r="N7">
-        <v>-2.8047916</v>
+        <v>-2.82374992</v>
       </c>
       <c r="O7">
-        <v>-0.7011978999999999</v>
+        <v>-0.7059374799999999</v>
       </c>
       <c r="P7">
-        <v>-2.1035937</v>
+        <v>-2.11781244</v>
       </c>
       <c r="Q7">
-        <v>3.5764063</v>
+        <v>3.56218756</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1252578672684656</v>
+        <v>0.1261031637287685</v>
       </c>
       <c r="T7">
-        <v>1.548781727912968</v>
+        <v>1.565258129273744</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-7.147257773895577</v>
+        <v>-5.956048144912979</v>
       </c>
       <c r="W7">
-        <v>1.921123383084577</v>
+        <v>1.64023615257048</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1986,7 +1997,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-28.58903109558231</v>
+        <v>-23.82419257965192</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1994,22 +2005,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2169511430592712</v>
+        <v>0.2188511430592712</v>
       </c>
       <c r="C8">
-        <v>2.130006663960449</v>
+        <v>2.020923971816516</v>
       </c>
       <c r="D8">
-        <v>2.612406663960449</v>
+        <v>2.583723971816516</v>
       </c>
       <c r="E8">
-        <v>0.4823999999999999</v>
+        <v>0.5627999999999999</v>
       </c>
       <c r="F8">
-        <v>0.4823999999999999</v>
+        <v>0.5627999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2030,37 +2041,37 @@
         <v>-2.71</v>
       </c>
       <c r="M8">
-        <v>0.11374992</v>
+        <v>0.13270824</v>
       </c>
       <c r="N8">
-        <v>-2.82374992</v>
+        <v>-2.842708239999999</v>
       </c>
       <c r="O8">
-        <v>-0.7059374799999999</v>
+        <v>-0.7106770599999999</v>
       </c>
       <c r="P8">
-        <v>-2.11781244</v>
+        <v>-2.132031179999999</v>
       </c>
       <c r="Q8">
-        <v>3.56218756</v>
+        <v>3.54796882</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1261031637287685</v>
+        <v>0.1269666386075724</v>
       </c>
       <c r="T8">
-        <v>1.565258129273744</v>
+        <v>1.58208886184658</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-5.95604814491298</v>
+        <v>-5.105184124211126</v>
       </c>
       <c r="W8">
-        <v>1.640236152570481</v>
+        <v>1.439602416488984</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -2068,7 +2079,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-23.82419257965192</v>
+        <v>-20.4207364968445</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2076,22 +2087,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2188511430592712</v>
+        <v>0.2207511430592712</v>
       </c>
       <c r="C9">
-        <v>2.020923971816516</v>
+        <v>1.91246427777503</v>
       </c>
       <c r="D9">
-        <v>2.583723971816516</v>
+        <v>2.55566427777503</v>
       </c>
       <c r="E9">
-        <v>0.5628</v>
+        <v>0.6432</v>
       </c>
       <c r="F9">
-        <v>0.5628</v>
+        <v>0.6432</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2112,37 +2123,37 @@
         <v>-2.71</v>
       </c>
       <c r="M9">
-        <v>0.13270824</v>
+        <v>0.15166656</v>
       </c>
       <c r="N9">
-        <v>-2.842708239999999</v>
+        <v>-2.86166656</v>
       </c>
       <c r="O9">
-        <v>-0.7106770599999999</v>
+        <v>-0.7154166399999999</v>
       </c>
       <c r="P9">
-        <v>-2.132031179999999</v>
+        <v>-2.14624992</v>
       </c>
       <c r="Q9">
-        <v>3.54796882</v>
+        <v>3.53375008</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1269666386075724</v>
+        <v>0.1278488846793938</v>
       </c>
       <c r="T9">
-        <v>1.582088861846581</v>
+        <v>1.59928547991013</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-5.105184124211125</v>
+        <v>-4.467036108684735</v>
       </c>
       <c r="W9">
-        <v>1.439602416488983</v>
+        <v>1.289127114427861</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2150,7 +2161,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-20.4207364968445</v>
+        <v>-17.86814443473894</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2158,22 +2169,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2207511430592712</v>
+        <v>0.2226511430592712</v>
       </c>
       <c r="C10">
-        <v>1.91246427777503</v>
+        <v>1.804607502298349</v>
       </c>
       <c r="D10">
-        <v>2.55566427777503</v>
+        <v>2.528207502298349</v>
       </c>
       <c r="E10">
-        <v>0.6432</v>
+        <v>0.7235999999999999</v>
       </c>
       <c r="F10">
-        <v>0.6432</v>
+        <v>0.7235999999999999</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2194,37 +2205,37 @@
         <v>-2.71</v>
       </c>
       <c r="M10">
-        <v>0.15166656</v>
+        <v>0.17062488</v>
       </c>
       <c r="N10">
-        <v>-2.86166656</v>
+        <v>-2.88062488</v>
       </c>
       <c r="O10">
-        <v>-0.7154166399999999</v>
+        <v>-0.7201562199999999</v>
       </c>
       <c r="P10">
-        <v>-2.14624992</v>
+        <v>-2.16046866</v>
       </c>
       <c r="Q10">
-        <v>3.53375008</v>
+        <v>3.51953134</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1278488846793938</v>
+        <v>0.1287505207747718</v>
       </c>
       <c r="T10">
-        <v>1.59928547991013</v>
+        <v>1.616860045623429</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-4.467036108684735</v>
+        <v>-3.97069876327532</v>
       </c>
       <c r="W10">
-        <v>1.289127114427861</v>
+        <v>1.172090768380321</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2232,7 +2243,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-17.86814443473894</v>
+        <v>-15.88279505310128</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2240,22 +2251,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2226511430592712</v>
+        <v>0.2245511430592712</v>
       </c>
       <c r="C11">
-        <v>1.804607502298349</v>
+        <v>1.697334419574767</v>
       </c>
       <c r="D11">
-        <v>2.528207502298349</v>
+        <v>2.501334419574766</v>
       </c>
       <c r="E11">
-        <v>0.7235999999999999</v>
+        <v>0.8039999999999998</v>
       </c>
       <c r="F11">
-        <v>0.7235999999999999</v>
+        <v>0.8039999999999998</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2276,37 +2287,37 @@
         <v>-2.71</v>
       </c>
       <c r="M11">
-        <v>0.17062488</v>
+        <v>0.1895832</v>
       </c>
       <c r="N11">
-        <v>-2.88062488</v>
+        <v>-2.899583199999999</v>
       </c>
       <c r="O11">
-        <v>-0.7201562199999999</v>
+        <v>-0.7248957999999999</v>
       </c>
       <c r="P11">
-        <v>-2.16046866</v>
+        <v>-2.1746874</v>
       </c>
       <c r="Q11">
-        <v>3.51953134</v>
+        <v>3.5053126</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1287505207747718</v>
+        <v>0.1296721932278248</v>
       </c>
       <c r="T11">
-        <v>1.616860045623429</v>
+        <v>1.634825157241466</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-3.97069876327532</v>
+        <v>-3.573628886947788</v>
       </c>
       <c r="W11">
-        <v>1.172090768380321</v>
+        <v>1.078461691542288</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2314,7 +2325,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-15.88279505310128</v>
+        <v>-14.29451554779115</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2322,22 +2333,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2245511430592712</v>
+        <v>0.2264511430592712</v>
       </c>
       <c r="C12">
-        <v>1.697334419574767</v>
+        <v>1.590626612623151</v>
       </c>
       <c r="D12">
-        <v>2.501334419574766</v>
+        <v>2.475026612623151</v>
       </c>
       <c r="E12">
-        <v>0.8039999999999999</v>
+        <v>0.8844</v>
       </c>
       <c r="F12">
-        <v>0.8039999999999999</v>
+        <v>0.8844</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2358,37 +2369,37 @@
         <v>-2.71</v>
       </c>
       <c r="M12">
-        <v>0.1895832</v>
+        <v>0.20854152</v>
       </c>
       <c r="N12">
-        <v>-2.899583199999999</v>
+        <v>-2.918541519999999</v>
       </c>
       <c r="O12">
-        <v>-0.7248957999999999</v>
+        <v>-0.7296353799999998</v>
       </c>
       <c r="P12">
-        <v>-2.1746874</v>
+        <v>-2.188906139999999</v>
       </c>
       <c r="Q12">
-        <v>3.5053126</v>
+        <v>3.49109386</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1296721932278248</v>
+        <v>0.1306145774213959</v>
       </c>
       <c r="T12">
-        <v>1.634825157241466</v>
+        <v>1.653193979232944</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-3.573628886947788</v>
+        <v>-3.248753533588898</v>
       </c>
       <c r="W12">
-        <v>1.078461691542288</v>
+        <v>1.001856083220262</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2396,7 +2407,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-14.29451554779115</v>
+        <v>-12.99501413435559</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2404,22 +2415,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2264511430592712</v>
+        <v>0.2283511430592712</v>
       </c>
       <c r="C13">
-        <v>1.590626612623151</v>
+        <v>1.48446643120124</v>
       </c>
       <c r="D13">
-        <v>2.475026612623151</v>
+        <v>2.44926643120124</v>
       </c>
       <c r="E13">
-        <v>0.8844</v>
+        <v>0.9647999999999999</v>
       </c>
       <c r="F13">
-        <v>0.8844</v>
+        <v>0.9647999999999999</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2440,37 +2451,37 @@
         <v>-2.71</v>
       </c>
       <c r="M13">
-        <v>0.20854152</v>
+        <v>0.22749984</v>
       </c>
       <c r="N13">
-        <v>-2.918541519999999</v>
+        <v>-2.93749984</v>
       </c>
       <c r="O13">
-        <v>-0.7296353799999998</v>
+        <v>-0.7343749599999999</v>
       </c>
       <c r="P13">
-        <v>-2.188906139999999</v>
+        <v>-2.20312488</v>
       </c>
       <c r="Q13">
-        <v>3.49109386</v>
+        <v>3.47687512</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1306145774213959</v>
+        <v>0.1315783794375481</v>
       </c>
       <c r="T13">
-        <v>1.653193979232944</v>
+        <v>1.6719802744515</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-3.248753533588898</v>
+        <v>-2.97802407245649</v>
       </c>
       <c r="W13">
-        <v>1.001856083220262</v>
+        <v>0.9380180762852404</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2478,7 +2489,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-12.99501413435559</v>
+        <v>-11.91209628982596</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2486,22 +2497,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2283511430592712</v>
+        <v>0.2302511430592712</v>
       </c>
       <c r="C14">
-        <v>1.48446643120124</v>
+        <v>1.378836952315404</v>
       </c>
       <c r="D14">
-        <v>2.44926643120124</v>
+        <v>2.424036952315404</v>
       </c>
       <c r="E14">
-        <v>0.9647999999999999</v>
+        <v>1.0452</v>
       </c>
       <c r="F14">
-        <v>0.9647999999999999</v>
+        <v>1.0452</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2522,37 +2533,37 @@
         <v>-2.71</v>
       </c>
       <c r="M14">
-        <v>0.22749984</v>
+        <v>0.24645816</v>
       </c>
       <c r="N14">
-        <v>-2.93749984</v>
+        <v>-2.95645816</v>
       </c>
       <c r="O14">
-        <v>-0.7343749599999999</v>
+        <v>-0.7391145399999999</v>
       </c>
       <c r="P14">
-        <v>-2.20312488</v>
+        <v>-2.217343619999999</v>
       </c>
       <c r="Q14">
-        <v>3.47687512</v>
+        <v>3.46265638</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1315783794375481</v>
+        <v>0.1325643378218878</v>
       </c>
       <c r="T14">
-        <v>1.6719802744515</v>
+        <v>1.691198438525655</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-2.97802407245649</v>
+        <v>-2.748945297652145</v>
       </c>
       <c r="W14">
-        <v>0.9380180762852404</v>
+        <v>0.8840013011863758</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2560,7 +2571,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-11.91209628982596</v>
+        <v>-10.99578119060858</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2568,22 +2579,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2302511430592712</v>
+        <v>0.2321511430592712</v>
       </c>
       <c r="C15">
-        <v>1.378836952315404</v>
+        <v>1.273721943146211</v>
       </c>
       <c r="D15">
-        <v>2.424036952315404</v>
+        <v>2.399321943146211</v>
       </c>
       <c r="E15">
-        <v>1.0452</v>
+        <v>1.1256</v>
       </c>
       <c r="F15">
-        <v>1.0452</v>
+        <v>1.1256</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2604,37 +2615,37 @@
         <v>-2.71</v>
       </c>
       <c r="M15">
-        <v>0.24645816</v>
+        <v>0.26541648</v>
       </c>
       <c r="N15">
-        <v>-2.95645816</v>
+        <v>-2.975416479999999</v>
       </c>
       <c r="O15">
-        <v>-0.7391145399999999</v>
+        <v>-0.7438541199999998</v>
       </c>
       <c r="P15">
-        <v>-2.217343619999999</v>
+        <v>-2.231562359999999</v>
       </c>
       <c r="Q15">
-        <v>3.46265638</v>
+        <v>3.44843764</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1325643378218878</v>
+        <v>0.1335732254709795</v>
       </c>
       <c r="T15">
-        <v>1.691198438525655</v>
+        <v>1.710863536648046</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-2.748945297652145</v>
+        <v>-2.552592062105563</v>
       </c>
       <c r="W15">
-        <v>0.8840013011863758</v>
+        <v>0.8377012082444917</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2642,7 +2653,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-10.99578119060858</v>
+        <v>-10.21036824842225</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2650,22 +2661,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2321511430592712</v>
+        <v>0.2340511430592712</v>
       </c>
       <c r="C16">
-        <v>1.273721943146211</v>
+        <v>1.169105826219142</v>
       </c>
       <c r="D16">
-        <v>2.399321943146211</v>
+        <v>2.375105826219142</v>
       </c>
       <c r="E16">
-        <v>1.1256</v>
+        <v>1.206</v>
       </c>
       <c r="F16">
-        <v>1.1256</v>
+        <v>1.206</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2686,37 +2697,37 @@
         <v>-2.71</v>
       </c>
       <c r="M16">
-        <v>0.26541648</v>
+        <v>0.2843748</v>
       </c>
       <c r="N16">
-        <v>-2.975416479999999</v>
+        <v>-2.9943748</v>
       </c>
       <c r="O16">
-        <v>-0.7438541199999998</v>
+        <v>-0.7485936999999999</v>
       </c>
       <c r="P16">
-        <v>-2.231562359999999</v>
+        <v>-2.2457811</v>
       </c>
       <c r="Q16">
-        <v>3.44843764</v>
+        <v>3.4342189</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1335732254709795</v>
+        <v>0.134605851652991</v>
       </c>
       <c r="T16">
-        <v>1.710863536648046</v>
+        <v>1.730991342961553</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-2.552592062105563</v>
+        <v>-2.382419257965192</v>
       </c>
       <c r="W16">
-        <v>0.8377012082444917</v>
+        <v>0.7975744610281923</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2724,7 +2735,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-10.21036824842225</v>
+        <v>-9.52967703186077</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2732,22 +2743,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2340511430592712</v>
+        <v>0.2359511430592712</v>
       </c>
       <c r="C17">
-        <v>1.169105826219142</v>
+        <v>1.064973646663378</v>
       </c>
       <c r="D17">
-        <v>2.375105826219142</v>
+        <v>2.351373646663378</v>
       </c>
       <c r="E17">
-        <v>1.206</v>
+        <v>1.2864</v>
       </c>
       <c r="F17">
-        <v>1.206</v>
+        <v>1.2864</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2768,37 +2779,37 @@
         <v>-2.71</v>
       </c>
       <c r="M17">
-        <v>0.2843747999999999</v>
+        <v>0.30333312</v>
       </c>
       <c r="N17">
-        <v>-2.994374799999999</v>
+        <v>-3.01333312</v>
       </c>
       <c r="O17">
-        <v>-0.7485936999999998</v>
+        <v>-0.7533332799999999</v>
       </c>
       <c r="P17">
-        <v>-2.245781099999999</v>
+        <v>-2.25999984</v>
       </c>
       <c r="Q17">
-        <v>3.4342189</v>
+        <v>3.42000016</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.134605851652991</v>
+        <v>0.1356630641726695</v>
       </c>
       <c r="T17">
-        <v>1.730991342961553</v>
+        <v>1.751598382758714</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-2.382419257965192</v>
+        <v>-2.233518054342368</v>
       </c>
       <c r="W17">
-        <v>0.7975744610281924</v>
+        <v>0.7624635572139303</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2806,7 +2817,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-9.52967703186077</v>
+        <v>-8.93407221736947</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2814,22 +2825,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2359511430592712</v>
+        <v>0.2378511430592712</v>
       </c>
       <c r="C18">
-        <v>1.064973646663378</v>
+        <v>0.9613110414141008</v>
       </c>
       <c r="D18">
-        <v>2.351373646663378</v>
+        <v>2.328111041414101</v>
       </c>
       <c r="E18">
-        <v>1.2864</v>
+        <v>1.3668</v>
       </c>
       <c r="F18">
-        <v>1.2864</v>
+        <v>1.3668</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2850,37 +2861,37 @@
         <v>-2.71</v>
       </c>
       <c r="M18">
-        <v>0.30333312</v>
+        <v>0.32229144</v>
       </c>
       <c r="N18">
-        <v>-3.01333312</v>
+        <v>-3.032291439999999</v>
       </c>
       <c r="O18">
-        <v>-0.7533332799999999</v>
+        <v>-0.7580728599999998</v>
       </c>
       <c r="P18">
-        <v>-2.25999984</v>
+        <v>-2.274218579999999</v>
       </c>
       <c r="Q18">
-        <v>3.42000016</v>
+        <v>3.40578142</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1356630641726695</v>
+        <v>0.1367457516928221</v>
       </c>
       <c r="T18">
-        <v>1.751598382758714</v>
+        <v>1.772701977731711</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-2.233518054342368</v>
+        <v>-2.102134639381052</v>
       </c>
       <c r="W18">
-        <v>0.7624635572139303</v>
+        <v>0.731483347966052</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2888,7 +2899,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-8.93407221736947</v>
+        <v>-8.408538557524205</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2896,22 +2907,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2378511430592712</v>
+        <v>0.2397511430592712</v>
       </c>
       <c r="C19">
-        <v>0.9613110414141008</v>
+        <v>0.8581042102249952</v>
       </c>
       <c r="D19">
-        <v>2.328111041414101</v>
+        <v>2.305304210224995</v>
       </c>
       <c r="E19">
-        <v>1.3668</v>
+        <v>1.4472</v>
       </c>
       <c r="F19">
-        <v>1.3668</v>
+        <v>1.4472</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2932,37 +2943,37 @@
         <v>-2.71</v>
       </c>
       <c r="M19">
-        <v>0.32229144</v>
+        <v>0.34124976</v>
       </c>
       <c r="N19">
-        <v>-3.032291439999999</v>
+        <v>-3.05124976</v>
       </c>
       <c r="O19">
-        <v>-0.7580728599999998</v>
+        <v>-0.7628124399999999</v>
       </c>
       <c r="P19">
-        <v>-2.274218579999999</v>
+        <v>-2.28843732</v>
       </c>
       <c r="Q19">
-        <v>3.40578142</v>
+        <v>3.39156268</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1367457516928221</v>
+        <v>0.1378548462256614</v>
       </c>
       <c r="T19">
-        <v>1.772701977731711</v>
+        <v>1.794320294533317</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-2.102134639381052</v>
+        <v>-1.98534938163766</v>
       </c>
       <c r="W19">
-        <v>0.731483347966052</v>
+        <v>0.7039453841901603</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2970,7 +2981,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-8.408538557524205</v>
+        <v>-7.94139752655064</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2978,22 +2989,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2397511430592712</v>
+        <v>0.2416511430592712</v>
       </c>
       <c r="C20">
-        <v>0.8581042102249945</v>
+        <v>0.7553398883680533</v>
       </c>
       <c r="D20">
-        <v>2.305304210224994</v>
+        <v>2.282939888368053</v>
       </c>
       <c r="E20">
-        <v>1.4472</v>
+        <v>1.5276</v>
       </c>
       <c r="F20">
-        <v>1.4472</v>
+        <v>1.5276</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3014,37 +3025,37 @@
         <v>-2.71</v>
       </c>
       <c r="M20">
-        <v>0.34124976</v>
+        <v>0.36020808</v>
       </c>
       <c r="N20">
-        <v>-3.051249759999999</v>
+        <v>-3.07020808</v>
       </c>
       <c r="O20">
-        <v>-0.7628124399999998</v>
+        <v>-0.7675520199999999</v>
       </c>
       <c r="P20">
-        <v>-2.288437319999999</v>
+        <v>-2.302656059999999</v>
       </c>
       <c r="Q20">
-        <v>3.39156268</v>
+        <v>3.37734394</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1378548462256614</v>
+        <v>0.1389913258086942</v>
       </c>
       <c r="T20">
-        <v>1.794320294533317</v>
+        <v>1.816472396934963</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-1.98534938163766</v>
+        <v>-1.880857308919889</v>
       </c>
       <c r="W20">
-        <v>0.7039453841901604</v>
+        <v>0.6793061534433098</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3052,7 +3063,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-7.94139752655064</v>
+        <v>-7.523429235679554</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3060,22 +3071,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2416511430592712</v>
+        <v>0.2435511430592712</v>
       </c>
       <c r="C21">
-        <v>0.7553398883680533</v>
+        <v>0.6530053209071756</v>
       </c>
       <c r="D21">
-        <v>2.282939888368053</v>
+        <v>2.261005320907175</v>
       </c>
       <c r="E21">
-        <v>1.5276</v>
+        <v>1.608</v>
       </c>
       <c r="F21">
-        <v>1.5276</v>
+        <v>1.608</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3096,37 +3107,37 @@
         <v>-2.71</v>
       </c>
       <c r="M21">
-        <v>0.36020808</v>
+        <v>0.3791664</v>
       </c>
       <c r="N21">
-        <v>-3.07020808</v>
+        <v>-3.089166399999999</v>
       </c>
       <c r="O21">
-        <v>-0.7675520199999999</v>
+        <v>-0.7722915999999999</v>
       </c>
       <c r="P21">
-        <v>-2.302656059999999</v>
+        <v>-2.316874799999999</v>
       </c>
       <c r="Q21">
-        <v>3.37734394</v>
+        <v>3.3631252</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1389913258086942</v>
+        <v>0.1401562173813029</v>
       </c>
       <c r="T21">
-        <v>1.816472396934963</v>
+        <v>1.83917830189665</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-1.880857308919889</v>
+        <v>-1.786814443473894</v>
       </c>
       <c r="W21">
-        <v>0.6793061534433098</v>
+        <v>0.6571308457711442</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3134,7 +3145,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-7.523429235679554</v>
+        <v>-7.147257773895577</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3142,22 +3153,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2435511430592712</v>
+        <v>0.2454511430592712</v>
       </c>
       <c r="C22">
-        <v>0.6530053209071756</v>
+        <v>0.5510882384407443</v>
       </c>
       <c r="D22">
-        <v>2.261005320907175</v>
+        <v>2.239488238440744</v>
       </c>
       <c r="E22">
-        <v>1.608</v>
+        <v>1.6884</v>
       </c>
       <c r="F22">
-        <v>1.608</v>
+        <v>1.6884</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3178,37 +3189,37 @@
         <v>-2.71</v>
       </c>
       <c r="M22">
-        <v>0.3791664</v>
+        <v>0.39812472</v>
       </c>
       <c r="N22">
-        <v>-3.089166399999999</v>
+        <v>-3.108124719999999</v>
       </c>
       <c r="O22">
-        <v>-0.7722915999999999</v>
+        <v>-0.7770311799999998</v>
       </c>
       <c r="P22">
-        <v>-2.316874799999999</v>
+        <v>-2.331093539999999</v>
       </c>
       <c r="Q22">
-        <v>3.3631252</v>
+        <v>3.34890646</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1401562173813029</v>
+        <v>0.1413505998798004</v>
       </c>
       <c r="T22">
-        <v>1.83917830189665</v>
+        <v>1.862459039895342</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-1.786814443473894</v>
+        <v>-1.701728041403709</v>
       </c>
       <c r="W22">
-        <v>0.6571308457711442</v>
+        <v>0.6370674721629945</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3216,7 +3227,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-7.147257773895577</v>
+        <v>-6.806912165614834</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3224,22 +3235,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2454511430592712</v>
+        <v>0.2473511430592712</v>
       </c>
       <c r="C23">
-        <v>0.5510882384407445</v>
+        <v>0.4495768342162287</v>
       </c>
       <c r="D23">
-        <v>2.239488238440744</v>
+        <v>2.218376834216229</v>
       </c>
       <c r="E23">
-        <v>1.6884</v>
+        <v>1.7688</v>
       </c>
       <c r="F23">
-        <v>1.6884</v>
+        <v>1.7688</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3260,37 +3271,37 @@
         <v>-2.71</v>
       </c>
       <c r="M23">
-        <v>0.3981247199999999</v>
+        <v>0.41708304</v>
       </c>
       <c r="N23">
-        <v>-3.108124719999999</v>
+        <v>-3.12708304</v>
       </c>
       <c r="O23">
-        <v>-0.7770311799999998</v>
+        <v>-0.7817707599999999</v>
       </c>
       <c r="P23">
-        <v>-2.331093539999999</v>
+        <v>-2.34531228</v>
       </c>
       <c r="Q23">
-        <v>3.34890646</v>
+        <v>3.33468772</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1413505998798004</v>
+        <v>0.1425756075705671</v>
       </c>
       <c r="T23">
-        <v>1.862459039895341</v>
+        <v>1.886336719894</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-1.701728041403709</v>
+        <v>-1.624376766794449</v>
       </c>
       <c r="W23">
-        <v>0.6370674721629946</v>
+        <v>0.6188280416101312</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3298,7 +3309,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-6.806912165614835</v>
+        <v>-6.497507067177796</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3306,22 +3317,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2473511430592712</v>
+        <v>0.2492511430592713</v>
       </c>
       <c r="C24">
-        <v>0.4495768342162287</v>
+        <v>0.3484597425271299</v>
       </c>
       <c r="D24">
-        <v>2.218376834216229</v>
+        <v>2.19765974252713</v>
       </c>
       <c r="E24">
-        <v>1.7688</v>
+        <v>1.8492</v>
       </c>
       <c r="F24">
-        <v>1.7688</v>
+        <v>1.8492</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3342,37 +3353,37 @@
         <v>-2.71</v>
       </c>
       <c r="M24">
-        <v>0.41708304</v>
+        <v>0.43604136</v>
       </c>
       <c r="N24">
-        <v>-3.12708304</v>
+        <v>-3.146041359999999</v>
       </c>
       <c r="O24">
-        <v>-0.7817707599999999</v>
+        <v>-0.7865103399999999</v>
       </c>
       <c r="P24">
-        <v>-2.34531228</v>
+        <v>-2.359531019999999</v>
       </c>
       <c r="Q24">
-        <v>3.33468772</v>
+        <v>3.32046898</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1425756075705671</v>
+        <v>0.1438324336429121</v>
       </c>
       <c r="T24">
-        <v>1.886336719894</v>
+        <v>1.910834599373143</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-1.624376766794449</v>
+        <v>-1.553751689977299</v>
       </c>
       <c r="W24">
-        <v>0.6188280416101312</v>
+        <v>0.6021746484966473</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3380,7 +3391,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-6.497507067177796</v>
+        <v>-6.215006759909197</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3388,22 +3399,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2492511430592713</v>
+        <v>0.2511511430592712</v>
       </c>
       <c r="C25">
-        <v>0.3484597425271299</v>
+        <v>0.2477260183092109</v>
       </c>
       <c r="D25">
-        <v>2.19765974252713</v>
+        <v>2.177326018309211</v>
       </c>
       <c r="E25">
-        <v>1.8492</v>
+        <v>1.9296</v>
       </c>
       <c r="F25">
-        <v>1.8492</v>
+        <v>1.9296</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3424,37 +3435,37 @@
         <v>-2.71</v>
       </c>
       <c r="M25">
-        <v>0.43604136</v>
+        <v>0.45499968</v>
       </c>
       <c r="N25">
-        <v>-3.146041359999999</v>
+        <v>-3.164999679999999</v>
       </c>
       <c r="O25">
-        <v>-0.7865103399999999</v>
+        <v>-0.7912499199999998</v>
       </c>
       <c r="P25">
-        <v>-2.359531019999999</v>
+        <v>-2.373749759999999</v>
       </c>
       <c r="Q25">
-        <v>3.32046898</v>
+        <v>3.30625024</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1438324336429121</v>
+        <v>0.145122334085582</v>
       </c>
       <c r="T25">
-        <v>1.910834599373143</v>
+        <v>1.93597715989121</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-1.553751689977299</v>
+        <v>-1.489012036228245</v>
       </c>
       <c r="W25">
-        <v>0.6021746484966473</v>
+        <v>0.5869090381426202</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3462,7 +3473,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-6.215006759909197</v>
+        <v>-5.956048144912979</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3470,22 +3481,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2511511430592712</v>
+        <v>0.2530511430592712</v>
       </c>
       <c r="C26">
-        <v>0.247726018309212</v>
+        <v>0.1473651178590534</v>
       </c>
       <c r="D26">
-        <v>2.177326018309212</v>
+        <v>2.157365117859053</v>
       </c>
       <c r="E26">
-        <v>1.9296</v>
+        <v>2.01</v>
       </c>
       <c r="F26">
-        <v>1.9296</v>
+        <v>2.01</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3506,37 +3517,37 @@
         <v>-2.71</v>
       </c>
       <c r="M26">
-        <v>0.45499968</v>
+        <v>0.473958</v>
       </c>
       <c r="N26">
-        <v>-3.164999679999999</v>
+        <v>-3.183958</v>
       </c>
       <c r="O26">
-        <v>-0.7912499199999998</v>
+        <v>-0.7959894999999999</v>
       </c>
       <c r="P26">
-        <v>-2.373749759999999</v>
+        <v>-2.387968499999999</v>
       </c>
       <c r="Q26">
-        <v>3.30625024</v>
+        <v>3.2920315</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.145122334085582</v>
+        <v>0.1464466318733898</v>
       </c>
       <c r="T26">
-        <v>1.93597715989121</v>
+        <v>1.96179018868976</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-1.489012036228245</v>
+        <v>-1.429451554779115</v>
       </c>
       <c r="W26">
-        <v>0.5869090381426202</v>
+        <v>0.5728646766169154</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3544,7 +3555,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-5.95604814491298</v>
+        <v>-5.717806219116461</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3552,22 +3563,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2530511430592712</v>
+        <v>0.2549511430592711</v>
       </c>
       <c r="C27">
-        <v>0.1473651178590534</v>
+        <v>0.04736688060356586</v>
       </c>
       <c r="D27">
-        <v>2.157365117859053</v>
+        <v>2.137766880603566</v>
       </c>
       <c r="E27">
-        <v>2.01</v>
+        <v>2.0904</v>
       </c>
       <c r="F27">
-        <v>2.01</v>
+        <v>2.0904</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3588,37 +3599,37 @@
         <v>-2.71</v>
       </c>
       <c r="M27">
-        <v>0.473958</v>
+        <v>0.49291632</v>
       </c>
       <c r="N27">
-        <v>-3.183958</v>
+        <v>-3.202916319999999</v>
       </c>
       <c r="O27">
-        <v>-0.7959894999999999</v>
+        <v>-0.8007290799999999</v>
       </c>
       <c r="P27">
-        <v>-2.387968499999999</v>
+        <v>-2.40218724</v>
       </c>
       <c r="Q27">
-        <v>3.2920315</v>
+        <v>3.27781276</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1464466318733898</v>
+        <v>0.1478067214933005</v>
       </c>
       <c r="T27">
-        <v>1.96179018868976</v>
+        <v>1.988300866915297</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-1.429451554779115</v>
+        <v>-1.374472648826072</v>
       </c>
       <c r="W27">
-        <v>0.5728646766169154</v>
+        <v>0.5599006505931878</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3626,7 +3637,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-5.717806219116461</v>
+        <v>-5.497890595304289</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3634,22 +3645,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2549511430592711</v>
+        <v>0.2568511430592712</v>
       </c>
       <c r="C28">
-        <v>0.04736688060356586</v>
+        <v>-0.05227848814578095</v>
       </c>
       <c r="D28">
-        <v>2.137766880603566</v>
+        <v>2.118521511854219</v>
       </c>
       <c r="E28">
-        <v>2.0904</v>
+        <v>2.1708</v>
       </c>
       <c r="F28">
-        <v>2.0904</v>
+        <v>2.1708</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3670,37 +3681,37 @@
         <v>-2.71</v>
       </c>
       <c r="M28">
-        <v>0.49291632</v>
+        <v>0.5118746399999999</v>
       </c>
       <c r="N28">
-        <v>-3.202916319999999</v>
+        <v>-3.221874639999999</v>
       </c>
       <c r="O28">
-        <v>-0.8007290799999999</v>
+        <v>-0.8054686599999998</v>
       </c>
       <c r="P28">
-        <v>-2.40218724</v>
+        <v>-2.41640598</v>
       </c>
       <c r="Q28">
-        <v>3.27781276</v>
+        <v>3.26359402</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1478067214933005</v>
+        <v>0.1492040738425238</v>
       </c>
       <c r="T28">
-        <v>1.988300866915297</v>
+        <v>2.015537865092219</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-1.374472648826072</v>
+        <v>-1.323566254425107</v>
       </c>
       <c r="W28">
-        <v>0.5599006505931878</v>
+        <v>0.5478969227934402</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3708,7 +3719,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-5.497890595304289</v>
+        <v>-5.294265017700427</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3716,22 +3727,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2568511430592712</v>
+        <v>0.2587511430592712</v>
       </c>
       <c r="C29">
-        <v>-0.05227848814578095</v>
+        <v>-0.151580433515488</v>
       </c>
       <c r="D29">
-        <v>2.118521511854219</v>
+        <v>2.099619566484512</v>
       </c>
       <c r="E29">
-        <v>2.1708</v>
+        <v>2.2512</v>
       </c>
       <c r="F29">
-        <v>2.1708</v>
+        <v>2.2512</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3752,37 +3763,37 @@
         <v>-2.71</v>
       </c>
       <c r="M29">
-        <v>0.5118746399999999</v>
+        <v>0.53083296</v>
       </c>
       <c r="N29">
-        <v>-3.221874639999999</v>
+        <v>-3.24083296</v>
       </c>
       <c r="O29">
-        <v>-0.8054686599999998</v>
+        <v>-0.8102082399999999</v>
       </c>
       <c r="P29">
-        <v>-2.41640598</v>
+        <v>-2.43062472</v>
       </c>
       <c r="Q29">
-        <v>3.26359402</v>
+        <v>3.24937528</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1492040738425238</v>
+        <v>0.150640241534781</v>
       </c>
       <c r="T29">
-        <v>2.015537865092219</v>
+        <v>2.043531446551833</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-1.323566254425107</v>
+        <v>-1.276296031052781</v>
       </c>
       <c r="W29">
-        <v>0.5478969227934402</v>
+        <v>0.5367506041222458</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3790,7 +3801,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-5.294265017700427</v>
+        <v>-5.105184124211125</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3798,22 +3809,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2587511430592712</v>
+        <v>0.2606511430592712</v>
       </c>
       <c r="C30">
-        <v>-0.151580433515488</v>
+        <v>-0.2505480665264983</v>
       </c>
       <c r="D30">
-        <v>2.099619566484512</v>
+        <v>2.081051933473502</v>
       </c>
       <c r="E30">
-        <v>2.2512</v>
+        <v>2.3316</v>
       </c>
       <c r="F30">
-        <v>2.2512</v>
+        <v>2.3316</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3834,37 +3845,37 @@
         <v>-2.71</v>
       </c>
       <c r="M30">
-        <v>0.53083296</v>
+        <v>0.54979128</v>
       </c>
       <c r="N30">
-        <v>-3.24083296</v>
+        <v>-3.25979128</v>
       </c>
       <c r="O30">
-        <v>-0.8102082399999999</v>
+        <v>-0.8149478199999999</v>
       </c>
       <c r="P30">
-        <v>-2.43062472</v>
+        <v>-2.44484346</v>
       </c>
       <c r="Q30">
-        <v>3.24937528</v>
+        <v>3.23515654</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.150640241534781</v>
+        <v>0.1521168646549892</v>
       </c>
       <c r="T30">
-        <v>2.043531446551833</v>
+        <v>2.072313579601859</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-1.276296031052781</v>
+        <v>-1.232285823085444</v>
       </c>
       <c r="W30">
-        <v>0.5367506041222458</v>
+        <v>0.5263729970835478</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3872,7 +3883,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-5.105184124211125</v>
+        <v>-4.929143292341776</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3880,22 +3891,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2606511430592712</v>
+        <v>0.2625511430592712</v>
       </c>
       <c r="C31">
-        <v>-0.2505480665264979</v>
+        <v>-0.3491901787377287</v>
       </c>
       <c r="D31">
-        <v>2.081051933473502</v>
+        <v>2.062809821262271</v>
       </c>
       <c r="E31">
-        <v>2.331599999999999</v>
+        <v>2.411999999999999</v>
       </c>
       <c r="F31">
-        <v>2.331599999999999</v>
+        <v>2.411999999999999</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3916,37 +3927,37 @@
         <v>-2.71</v>
       </c>
       <c r="M31">
-        <v>0.5497912799999999</v>
+        <v>0.5687495999999999</v>
       </c>
       <c r="N31">
-        <v>-3.25979128</v>
+        <v>-3.278749599999999</v>
       </c>
       <c r="O31">
-        <v>-0.8149478199999999</v>
+        <v>-0.8196873999999998</v>
       </c>
       <c r="P31">
-        <v>-2.44484346</v>
+        <v>-2.4590622</v>
       </c>
       <c r="Q31">
-        <v>3.23515654</v>
+        <v>3.2209378</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1521168646549892</v>
+        <v>0.1536356770072034</v>
       </c>
       <c r="T31">
-        <v>2.072313579601859</v>
+        <v>2.101918059310457</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-1.232285823085444</v>
+        <v>-1.191209628982596</v>
       </c>
       <c r="W31">
-        <v>0.5263729970835478</v>
+        <v>0.5166872305140963</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3954,7 +3965,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-4.929143292341778</v>
+        <v>-4.764838515930385</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3962,22 +3973,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2625511430592712</v>
+        <v>0.2644511430592712</v>
       </c>
       <c r="C32">
-        <v>-0.3491901787377287</v>
+        <v>-0.4475152561261222</v>
       </c>
       <c r="D32">
-        <v>2.062809821262271</v>
+        <v>2.044884743873877</v>
       </c>
       <c r="E32">
-        <v>2.411999999999999</v>
+        <v>2.4924</v>
       </c>
       <c r="F32">
-        <v>2.411999999999999</v>
+        <v>2.4924</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3998,37 +4009,37 @@
         <v>-2.71</v>
       </c>
       <c r="M32">
-        <v>0.5687495999999999</v>
+        <v>0.5877079199999999</v>
       </c>
       <c r="N32">
-        <v>-3.278749599999999</v>
+        <v>-3.29770792</v>
       </c>
       <c r="O32">
-        <v>-0.8196873999999998</v>
+        <v>-0.8244269799999999</v>
       </c>
       <c r="P32">
-        <v>-2.4590622</v>
+        <v>-2.47328094</v>
       </c>
       <c r="Q32">
-        <v>3.2209378</v>
+        <v>3.20671906</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1536356770072034</v>
+        <v>0.1551985129058585</v>
       </c>
       <c r="T32">
-        <v>2.101918059310457</v>
+        <v>2.132380639880174</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-1.191209628982596</v>
+        <v>-1.152783511918641</v>
       </c>
       <c r="W32">
-        <v>0.5166872305140963</v>
+        <v>0.5076263521104156</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4036,7 +4047,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-4.764838515930385</v>
+        <v>-4.611134047674566</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4044,22 +4055,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2644511430592712</v>
+        <v>0.2663511430592712</v>
       </c>
       <c r="C33">
-        <v>-0.4475152561261222</v>
+        <v>-0.5455314922492613</v>
       </c>
       <c r="D33">
-        <v>2.044884743873877</v>
+        <v>2.027268507750739</v>
       </c>
       <c r="E33">
-        <v>2.4924</v>
+        <v>2.5728</v>
       </c>
       <c r="F33">
-        <v>2.4924</v>
+        <v>2.5728</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4080,37 +4091,37 @@
         <v>-2.71</v>
       </c>
       <c r="M33">
-        <v>0.5877079199999999</v>
+        <v>0.60666624</v>
       </c>
       <c r="N33">
-        <v>-3.29770792</v>
+        <v>-3.31666624</v>
       </c>
       <c r="O33">
-        <v>-0.8244269799999999</v>
+        <v>-0.8291665599999999</v>
       </c>
       <c r="P33">
-        <v>-2.47328094</v>
+        <v>-2.48749968</v>
       </c>
       <c r="Q33">
-        <v>3.20671906</v>
+        <v>3.19250032</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1551985129058585</v>
+        <v>0.1568073145662387</v>
       </c>
       <c r="T33">
-        <v>2.132380639880174</v>
+        <v>2.163739178701941</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-1.152783511918641</v>
+        <v>-1.116759027171184</v>
       </c>
       <c r="W33">
-        <v>0.5076263521104156</v>
+        <v>0.4991317786069651</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4118,7 +4129,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-4.611134047674566</v>
+        <v>-4.467036108684735</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4126,22 +4137,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2663511430592712</v>
+        <v>0.2682511430592712</v>
       </c>
       <c r="C34">
-        <v>-0.5455314922492613</v>
+        <v>-0.643246800733428</v>
       </c>
       <c r="D34">
-        <v>2.027268507750739</v>
+        <v>2.009953199266572</v>
       </c>
       <c r="E34">
-        <v>2.5728</v>
+        <v>2.6532</v>
       </c>
       <c r="F34">
-        <v>2.5728</v>
+        <v>2.6532</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4162,37 +4173,37 @@
         <v>-2.71</v>
       </c>
       <c r="M34">
-        <v>0.60666624</v>
+        <v>0.62562456</v>
       </c>
       <c r="N34">
-        <v>-3.31666624</v>
+        <v>-3.335624559999999</v>
       </c>
       <c r="O34">
-        <v>-0.8291665599999999</v>
+        <v>-0.8339061399999999</v>
       </c>
       <c r="P34">
-        <v>-2.48749968</v>
+        <v>-2.50171842</v>
       </c>
       <c r="Q34">
-        <v>3.19250032</v>
+        <v>3.17828158</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1568073145662387</v>
+        <v>0.1584641401567796</v>
       </c>
       <c r="T34">
-        <v>2.163739178701941</v>
+        <v>2.196033793309433</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-1.116759027171184</v>
+        <v>-1.082917844529633</v>
       </c>
       <c r="W34">
-        <v>0.4991317786069651</v>
+        <v>0.4911520277400875</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4200,7 +4211,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-4.467036108684735</v>
+        <v>-4.33167137811853</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4208,22 +4219,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2682511430592712</v>
+        <v>0.2701511430592712</v>
       </c>
       <c r="C35">
-        <v>-0.643246800733428</v>
+        <v>-0.7406688271271042</v>
       </c>
       <c r="D35">
-        <v>2.009953199266572</v>
+        <v>1.992931172872896</v>
       </c>
       <c r="E35">
-        <v>2.6532</v>
+        <v>2.7336</v>
       </c>
       <c r="F35">
-        <v>2.6532</v>
+        <v>2.7336</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4244,37 +4255,37 @@
         <v>-2.71</v>
       </c>
       <c r="M35">
-        <v>0.62562456</v>
+        <v>0.6445828800000001</v>
       </c>
       <c r="N35">
-        <v>-3.335624559999999</v>
+        <v>-3.35458288</v>
       </c>
       <c r="O35">
-        <v>-0.8339061399999999</v>
+        <v>-0.8386457199999999</v>
       </c>
       <c r="P35">
-        <v>-2.50171842</v>
+        <v>-2.51593716</v>
       </c>
       <c r="Q35">
-        <v>3.17828158</v>
+        <v>3.16406284</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1584641401567796</v>
+        <v>0.1601711725833975</v>
       </c>
       <c r="T35">
-        <v>2.196033793309433</v>
+        <v>2.229307032602</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-1.082917844529633</v>
+        <v>-1.051067319690526</v>
       </c>
       <c r="W35">
-        <v>0.4911520277400875</v>
+        <v>0.483641673983026</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4282,7 +4293,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-4.33167137811853</v>
+        <v>-4.204269278762103</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4290,22 +4301,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2701511430592712</v>
+        <v>0.2720511430592712</v>
       </c>
       <c r="C36">
-        <v>-0.7406688271271042</v>
+        <v>-0.8378049601572324</v>
       </c>
       <c r="D36">
-        <v>1.992931172872896</v>
+        <v>1.976195039842768</v>
       </c>
       <c r="E36">
-        <v>2.7336</v>
+        <v>2.814</v>
       </c>
       <c r="F36">
-        <v>2.7336</v>
+        <v>2.814</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4326,37 +4337,37 @@
         <v>-2.71</v>
       </c>
       <c r="M36">
-        <v>0.6445828800000001</v>
+        <v>0.6635412000000001</v>
       </c>
       <c r="N36">
-        <v>-3.35458288</v>
+        <v>-3.3735412</v>
       </c>
       <c r="O36">
-        <v>-0.8386457199999999</v>
+        <v>-0.8433852999999999</v>
       </c>
       <c r="P36">
-        <v>-2.51593716</v>
+        <v>-2.5301559</v>
       </c>
       <c r="Q36">
-        <v>3.16406284</v>
+        <v>3.1498441</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1601711725833975</v>
+        <v>0.1619307290846805</v>
       </c>
       <c r="T36">
-        <v>2.229307032602</v>
+        <v>2.2636040638728</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-1.051067319690526</v>
+        <v>-1.021036824842225</v>
       </c>
       <c r="W36">
-        <v>0.483641673983026</v>
+        <v>0.4765604832977967</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4364,7 +4375,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-4.204269278762103</v>
+        <v>-4.0841472993689</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4372,22 +4383,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2720511430592712</v>
+        <v>0.2739511430592712</v>
       </c>
       <c r="C37">
-        <v>-0.8378049601572324</v>
+        <v>-0.9346623424230132</v>
       </c>
       <c r="D37">
-        <v>1.976195039842768</v>
+        <v>1.959737657576987</v>
       </c>
       <c r="E37">
-        <v>2.814</v>
+        <v>2.8944</v>
       </c>
       <c r="F37">
-        <v>2.814</v>
+        <v>2.8944</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4408,37 +4419,37 @@
         <v>-2.71</v>
       </c>
       <c r="M37">
-        <v>0.6635412000000001</v>
+        <v>0.68249952</v>
       </c>
       <c r="N37">
-        <v>-3.3735412</v>
+        <v>-3.392499519999999</v>
       </c>
       <c r="O37">
-        <v>-0.8433852999999999</v>
+        <v>-0.8481248799999999</v>
       </c>
       <c r="P37">
-        <v>-2.5301559</v>
+        <v>-2.54437464</v>
       </c>
       <c r="Q37">
-        <v>3.1498441</v>
+        <v>3.13562536</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1619307290846805</v>
+        <v>0.1637452717266287</v>
       </c>
       <c r="T37">
-        <v>2.2636040638728</v>
+        <v>2.298972877370812</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-1.021036824842225</v>
+        <v>-0.99267469081883</v>
       </c>
       <c r="W37">
-        <v>0.4765604832977967</v>
+        <v>0.4698726920950801</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4446,7 +4457,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-4.0841472993689</v>
+        <v>-3.97069876327532</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4454,22 +4465,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2739511430592712</v>
+        <v>0.2758511430592712</v>
       </c>
       <c r="C38">
-        <v>-0.9346623424230127</v>
+        <v>-1.031247880559795</v>
       </c>
       <c r="D38">
-        <v>1.959737657576987</v>
+        <v>1.943552119440204</v>
       </c>
       <c r="E38">
-        <v>2.8944</v>
+        <v>2.9748</v>
       </c>
       <c r="F38">
-        <v>2.8944</v>
+        <v>2.9748</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4490,37 +4501,37 @@
         <v>-2.71</v>
       </c>
       <c r="M38">
-        <v>0.6824995199999999</v>
+        <v>0.70145784</v>
       </c>
       <c r="N38">
-        <v>-3.392499519999999</v>
+        <v>-3.41145784</v>
       </c>
       <c r="O38">
-        <v>-0.8481248799999999</v>
+        <v>-0.8528644599999999</v>
       </c>
       <c r="P38">
-        <v>-2.54437464</v>
+        <v>-2.55859338</v>
       </c>
       <c r="Q38">
-        <v>3.13562536</v>
+        <v>3.12140662</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1637452717266287</v>
+        <v>0.1656174188968926</v>
       </c>
       <c r="T38">
-        <v>2.298972877370812</v>
+        <v>2.335464510344952</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-0.9926746908188301</v>
+        <v>-0.9658456451210238</v>
       </c>
       <c r="W38">
-        <v>0.4698726920950802</v>
+        <v>0.4635464031195374</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4528,7 +4539,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-3.970698763275321</v>
+        <v>-3.863382580484095</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4536,22 +4547,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2758511430592712</v>
+        <v>0.2777511430592712</v>
       </c>
       <c r="C39">
-        <v>-1.031247880559795</v>
+        <v>-1.127568254903425</v>
       </c>
       <c r="D39">
-        <v>1.943552119440204</v>
+        <v>1.927631745096575</v>
       </c>
       <c r="E39">
-        <v>2.9748</v>
+        <v>3.0552</v>
       </c>
       <c r="F39">
-        <v>2.9748</v>
+        <v>3.0552</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4572,37 +4583,37 @@
         <v>-2.71</v>
       </c>
       <c r="M39">
-        <v>0.70145784</v>
+        <v>0.72041616</v>
       </c>
       <c r="N39">
-        <v>-3.41145784</v>
+        <v>-3.43041616</v>
       </c>
       <c r="O39">
-        <v>-0.8528644599999999</v>
+        <v>-0.8576040399999999</v>
       </c>
       <c r="P39">
-        <v>-2.55859338</v>
+        <v>-2.57281212</v>
       </c>
       <c r="Q39">
-        <v>3.12140662</v>
+        <v>3.10718788</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1656174188968926</v>
+        <v>0.1675499579113586</v>
       </c>
       <c r="T39">
-        <v>2.335464510344952</v>
+        <v>2.37313329276987</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-0.9658456451210238</v>
+        <v>-0.9404286544599443</v>
       </c>
       <c r="W39">
-        <v>0.4635464031195374</v>
+        <v>0.4575530767216549</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4610,7 +4621,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-3.863382580484095</v>
+        <v>-3.761714617839777</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4618,22 +4629,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2777511430592712</v>
+        <v>0.2796511430592712</v>
       </c>
       <c r="C40">
-        <v>-1.127568254903425</v>
+        <v>-1.223629928683465</v>
       </c>
       <c r="D40">
-        <v>1.927631745096575</v>
+        <v>1.911970071316535</v>
       </c>
       <c r="E40">
-        <v>3.0552</v>
+        <v>3.1356</v>
       </c>
       <c r="F40">
-        <v>3.0552</v>
+        <v>3.1356</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4654,37 +4665,37 @@
         <v>-2.71</v>
       </c>
       <c r="M40">
-        <v>0.72041616</v>
+        <v>0.7393744799999999</v>
       </c>
       <c r="N40">
-        <v>-3.43041616</v>
+        <v>-3.449374479999999</v>
       </c>
       <c r="O40">
-        <v>-0.8576040399999999</v>
+        <v>-0.8623436199999999</v>
       </c>
       <c r="P40">
-        <v>-2.57281212</v>
+        <v>-2.58703086</v>
       </c>
       <c r="Q40">
-        <v>3.10718788</v>
+        <v>3.09296914</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1675499579113586</v>
+        <v>0.1695458588607252</v>
       </c>
       <c r="T40">
-        <v>2.37313329276987</v>
+        <v>2.412037117241508</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-0.9404286544599443</v>
+        <v>-0.9163150992173816</v>
       </c>
       <c r="W40">
-        <v>0.4575530767216549</v>
+        <v>0.4518671003954586</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4692,7 +4703,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-3.761714617839777</v>
+        <v>-3.665260396869527</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4700,22 +4711,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2796511430592712</v>
+        <v>0.2815511430592712</v>
       </c>
       <c r="C41">
-        <v>-1.223629928683465</v>
+        <v>-1.319439156771864</v>
       </c>
       <c r="D41">
-        <v>1.911970071316535</v>
+        <v>1.896560843228135</v>
       </c>
       <c r="E41">
-        <v>3.1356</v>
+        <v>3.216</v>
       </c>
       <c r="F41">
-        <v>3.1356</v>
+        <v>3.216</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4736,37 +4747,37 @@
         <v>-2.71</v>
       </c>
       <c r="M41">
-        <v>0.7393744799999999</v>
+        <v>0.7583327999999999</v>
       </c>
       <c r="N41">
-        <v>-3.449374479999999</v>
+        <v>-3.468332799999999</v>
       </c>
       <c r="O41">
-        <v>-0.8623436199999999</v>
+        <v>-0.8670831999999998</v>
       </c>
       <c r="P41">
-        <v>-2.58703086</v>
+        <v>-2.6012496</v>
       </c>
       <c r="Q41">
-        <v>3.09296914</v>
+        <v>3.0787504</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1695458588607252</v>
+        <v>0.1716082898417373</v>
       </c>
       <c r="T41">
-        <v>2.412037117241508</v>
+        <v>2.4522377358622</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-0.9163150992173816</v>
+        <v>-0.8934072217369471</v>
       </c>
       <c r="W41">
-        <v>0.4518671003954586</v>
+        <v>0.4464654228855721</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4774,7 +4785,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-3.665260396869527</v>
+        <v>-3.573628886947788</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4782,22 +4793,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2815511430592712</v>
+        <v>0.2834511430592712</v>
       </c>
       <c r="C42">
-        <v>-1.319439156771864</v>
+        <v>-1.415001994011972</v>
       </c>
       <c r="D42">
-        <v>1.896560843228135</v>
+        <v>1.881398005988027</v>
       </c>
       <c r="E42">
-        <v>3.216</v>
+        <v>3.2964</v>
       </c>
       <c r="F42">
-        <v>3.216</v>
+        <v>3.2964</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4818,37 +4829,37 @@
         <v>-2.71</v>
       </c>
       <c r="M42">
-        <v>0.7583327999999999</v>
+        <v>0.77729112</v>
       </c>
       <c r="N42">
-        <v>-3.468332799999999</v>
+        <v>-3.48729112</v>
       </c>
       <c r="O42">
-        <v>-0.8670831999999998</v>
+        <v>-0.8718227799999999</v>
       </c>
       <c r="P42">
-        <v>-2.6012496</v>
+        <v>-2.61546834</v>
       </c>
       <c r="Q42">
-        <v>3.0787504</v>
+        <v>3.06453166</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1716082898417373</v>
+        <v>0.1737406337373599</v>
       </c>
       <c r="T42">
-        <v>2.4522377358622</v>
+        <v>2.493801087317491</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-0.8934072217369471</v>
+        <v>-0.8716168016945824</v>
       </c>
       <c r="W42">
-        <v>0.4464654228855721</v>
+        <v>0.4413272418395826</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4856,7 +4867,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-3.573628886947788</v>
+        <v>-3.48646720677833</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4864,22 +4875,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2834511430592712</v>
+        <v>0.2853511430592712</v>
       </c>
       <c r="C43">
-        <v>-1.415001994011972</v>
+        <v>-1.510324303151165</v>
       </c>
       <c r="D43">
-        <v>1.881398005988027</v>
+        <v>1.866475696848835</v>
       </c>
       <c r="E43">
-        <v>3.2964</v>
+        <v>3.3768</v>
       </c>
       <c r="F43">
-        <v>3.2964</v>
+        <v>3.3768</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4900,37 +4911,37 @@
         <v>-2.71</v>
       </c>
       <c r="M43">
-        <v>0.77729112</v>
+        <v>0.79624944</v>
       </c>
       <c r="N43">
-        <v>-3.48729112</v>
+        <v>-3.506249439999999</v>
       </c>
       <c r="O43">
-        <v>-0.8718227799999999</v>
+        <v>-0.8765623599999999</v>
       </c>
       <c r="P43">
-        <v>-2.61546834</v>
+        <v>-2.62968708</v>
       </c>
       <c r="Q43">
-        <v>3.06453166</v>
+        <v>3.05031292</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1737406337373599</v>
+        <v>0.1759465067328316</v>
       </c>
       <c r="T43">
-        <v>2.493801087317491</v>
+        <v>2.536797657788483</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-0.8716168016945824</v>
+        <v>-0.8508640207018543</v>
       </c>
       <c r="W43">
-        <v>0.4413272418395826</v>
+        <v>0.4364337360814973</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4938,7 +4949,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-3.48646720677833</v>
+        <v>-3.403456082807417</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4946,22 +4957,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2853511430592712</v>
+        <v>0.2872511430592712</v>
       </c>
       <c r="C44">
-        <v>-1.510324303151165</v>
+        <v>-1.605411762398944</v>
       </c>
       <c r="D44">
-        <v>1.866475696848835</v>
+        <v>1.851788237601056</v>
       </c>
       <c r="E44">
-        <v>3.376799999999999</v>
+        <v>3.457199999999999</v>
       </c>
       <c r="F44">
-        <v>3.376799999999999</v>
+        <v>3.457199999999999</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4982,37 +4993,37 @@
         <v>-2.71</v>
       </c>
       <c r="M44">
-        <v>0.7962494399999999</v>
+        <v>0.8152077599999998</v>
       </c>
       <c r="N44">
-        <v>-3.506249439999999</v>
+        <v>-3.525207759999999</v>
       </c>
       <c r="O44">
-        <v>-0.8765623599999999</v>
+        <v>-0.8813019399999998</v>
       </c>
       <c r="P44">
-        <v>-2.62968708</v>
+        <v>-2.64390582</v>
       </c>
       <c r="Q44">
-        <v>3.05031292</v>
+        <v>3.03609418</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1759465067328316</v>
+        <v>0.178229778780776</v>
       </c>
       <c r="T44">
-        <v>2.536797657788482</v>
+        <v>2.581302879854947</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-0.8508640207018544</v>
+        <v>-0.8310764853366951</v>
       </c>
       <c r="W44">
-        <v>0.4364337360814973</v>
+        <v>0.4317678352423928</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5020,7 +5031,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-3.403456082807418</v>
+        <v>-3.32430594134678</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5028,22 +5039,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2872511430592712</v>
+        <v>0.2891511430592712</v>
       </c>
       <c r="C45">
-        <v>-1.605411762398944</v>
+        <v>-1.700269872630976</v>
       </c>
       <c r="D45">
-        <v>1.851788237601056</v>
+        <v>1.837330127369023</v>
       </c>
       <c r="E45">
-        <v>3.457199999999999</v>
+        <v>3.5376</v>
       </c>
       <c r="F45">
-        <v>3.457199999999999</v>
+        <v>3.5376</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -5064,37 +5075,37 @@
         <v>-2.71</v>
       </c>
       <c r="M45">
-        <v>0.8152077599999998</v>
+        <v>0.83416608</v>
       </c>
       <c r="N45">
-        <v>-3.525207759999999</v>
+        <v>-3.54416608</v>
       </c>
       <c r="O45">
-        <v>-0.8813019399999998</v>
+        <v>-0.8860415199999999</v>
       </c>
       <c r="P45">
-        <v>-2.64390582</v>
+        <v>-2.65812456</v>
       </c>
       <c r="Q45">
-        <v>3.03609418</v>
+        <v>3.02187544</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.178229778780776</v>
+        <v>0.1805945962590042</v>
       </c>
       <c r="T45">
-        <v>2.581302879854947</v>
+        <v>2.627397574138071</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-0.8310764853366951</v>
+        <v>-0.8121883833972245</v>
       </c>
       <c r="W45">
-        <v>0.4317678352423928</v>
+        <v>0.4273140208050656</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5102,7 +5113,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-3.32430594134678</v>
+        <v>-3.248753533588898</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5110,22 +5121,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2891511430592712</v>
+        <v>0.2910511430592712</v>
       </c>
       <c r="C46">
-        <v>-1.700269872630976</v>
+        <v>-1.794903964258257</v>
       </c>
       <c r="D46">
-        <v>1.837330127369023</v>
+        <v>1.823096035741743</v>
       </c>
       <c r="E46">
-        <v>3.5376</v>
+        <v>3.618</v>
       </c>
       <c r="F46">
-        <v>3.5376</v>
+        <v>3.618</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5146,37 +5157,37 @@
         <v>-2.71</v>
       </c>
       <c r="M46">
-        <v>0.83416608</v>
+        <v>0.8531244</v>
       </c>
       <c r="N46">
-        <v>-3.54416608</v>
+        <v>-3.5631244</v>
       </c>
       <c r="O46">
-        <v>-0.8860415199999999</v>
+        <v>-0.8907810999999999</v>
       </c>
       <c r="P46">
-        <v>-2.65812456</v>
+        <v>-2.6723433</v>
       </c>
       <c r="Q46">
-        <v>3.02187544</v>
+        <v>3.0076567</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1805945962590042</v>
+        <v>0.183045407100077</v>
       </c>
       <c r="T46">
-        <v>2.627397574138071</v>
+        <v>2.6751684391224</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-0.8121883833972245</v>
+        <v>-0.794139752655064</v>
       </c>
       <c r="W46">
-        <v>0.4273140208050656</v>
+        <v>0.4230581536760641</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5184,7 +5195,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-3.248753533588898</v>
+        <v>-3.176559010620256</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5192,22 +5203,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2910511430592712</v>
+        <v>0.2929511430592712</v>
       </c>
       <c r="C47">
-        <v>-1.794903964258257</v>
+        <v>-1.889319203779439</v>
       </c>
       <c r="D47">
-        <v>1.823096035741743</v>
+        <v>1.809080796220561</v>
       </c>
       <c r="E47">
-        <v>3.618</v>
+        <v>3.6984</v>
       </c>
       <c r="F47">
-        <v>3.618</v>
+        <v>3.6984</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5228,37 +5239,37 @@
         <v>-2.71</v>
       </c>
       <c r="M47">
-        <v>0.8531244</v>
+        <v>0.87208272</v>
       </c>
       <c r="N47">
-        <v>-3.5631244</v>
+        <v>-3.582082719999999</v>
       </c>
       <c r="O47">
-        <v>-0.8907810999999999</v>
+        <v>-0.8955206799999998</v>
       </c>
       <c r="P47">
-        <v>-2.6723433</v>
+        <v>-2.68656204</v>
       </c>
       <c r="Q47">
-        <v>3.0076567</v>
+        <v>2.99343796</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.183045407100077</v>
+        <v>0.1855869887130414</v>
       </c>
       <c r="T47">
-        <v>2.6751684391224</v>
+        <v>2.724708595402444</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-0.794139752655064</v>
+        <v>-0.7768758449886496</v>
       </c>
       <c r="W47">
-        <v>0.4230581536760641</v>
+        <v>0.4189873242483236</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5266,7 +5277,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-3.176559010620256</v>
+        <v>-3.107503379954598</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5274,22 +5285,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2929511430592712</v>
+        <v>0.2948511430592712</v>
       </c>
       <c r="C48">
-        <v>-1.889319203779439</v>
+        <v>-1.983520600033223</v>
       </c>
       <c r="D48">
-        <v>1.809080796220561</v>
+        <v>1.795279399966777</v>
       </c>
       <c r="E48">
-        <v>3.6984</v>
+        <v>3.7788</v>
       </c>
       <c r="F48">
-        <v>3.6984</v>
+        <v>3.7788</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5310,37 +5321,37 @@
         <v>-2.71</v>
       </c>
       <c r="M48">
-        <v>0.87208272</v>
+        <v>0.8910410400000001</v>
       </c>
       <c r="N48">
-        <v>-3.582082719999999</v>
+        <v>-3.60104104</v>
       </c>
       <c r="O48">
-        <v>-0.8955206799999998</v>
+        <v>-0.9002602599999999</v>
       </c>
       <c r="P48">
-        <v>-2.68656204</v>
+        <v>-2.70078078</v>
       </c>
       <c r="Q48">
-        <v>2.99343796</v>
+        <v>2.97921922</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1855869887130414</v>
+        <v>0.1882244790661176</v>
       </c>
       <c r="T48">
-        <v>2.724708595402444</v>
+        <v>2.776118191542113</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-0.7768758449886496</v>
+        <v>-0.7603465716910187</v>
       </c>
       <c r="W48">
-        <v>0.4189873242483236</v>
+        <v>0.4150897216047422</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5348,7 +5359,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-3.107503379954598</v>
+        <v>-3.041386286764075</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5356,22 +5367,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2948511430592712</v>
+        <v>0.2967511430592712</v>
       </c>
       <c r="C49">
-        <v>-1.983520600033223</v>
+        <v>-2.077513010166742</v>
       </c>
       <c r="D49">
-        <v>1.795279399966777</v>
+        <v>1.781686989833258</v>
       </c>
       <c r="E49">
-        <v>3.7788</v>
+        <v>3.8592</v>
       </c>
       <c r="F49">
-        <v>3.7788</v>
+        <v>3.8592</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5392,37 +5403,37 @@
         <v>-2.71</v>
       </c>
       <c r="M49">
-        <v>0.8910410400000001</v>
+        <v>0.90999936</v>
       </c>
       <c r="N49">
-        <v>-3.60104104</v>
+        <v>-3.61999936</v>
       </c>
       <c r="O49">
-        <v>-0.9002602599999999</v>
+        <v>-0.9049998399999999</v>
       </c>
       <c r="P49">
-        <v>-2.70078078</v>
+        <v>-2.71499952</v>
       </c>
       <c r="Q49">
-        <v>2.97921922</v>
+        <v>2.96500048</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1882244790661176</v>
+        <v>0.1909634113558507</v>
       </c>
       <c r="T49">
-        <v>2.776118191542113</v>
+        <v>2.829505079841</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-0.7603465716910187</v>
+        <v>-0.7445060181141224</v>
       </c>
       <c r="W49">
-        <v>0.4150897216047422</v>
+        <v>0.4113545190713101</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5430,7 +5441,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-3.041386286764075</v>
+        <v>-2.97802407245649</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5438,22 +5449,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2967511430592712</v>
+        <v>0.2986511430592712</v>
       </c>
       <c r="C50">
-        <v>-2.077513010166741</v>
+        <v>-2.17130114533483</v>
       </c>
       <c r="D50">
-        <v>1.781686989833258</v>
+        <v>1.768298854665169</v>
       </c>
       <c r="E50">
-        <v>3.8592</v>
+        <v>3.9396</v>
       </c>
       <c r="F50">
-        <v>3.8592</v>
+        <v>3.9396</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5474,37 +5485,37 @@
         <v>-2.71</v>
       </c>
       <c r="M50">
-        <v>0.9099993599999999</v>
+        <v>0.9289576799999999</v>
       </c>
       <c r="N50">
-        <v>-3.61999936</v>
+        <v>-3.638957679999999</v>
       </c>
       <c r="O50">
-        <v>-0.9049998399999999</v>
+        <v>-0.9097394199999999</v>
       </c>
       <c r="P50">
-        <v>-2.71499952</v>
+        <v>-2.72921826</v>
       </c>
       <c r="Q50">
-        <v>2.96500048</v>
+        <v>2.95078174</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1909634113558507</v>
+        <v>0.193809752754985</v>
       </c>
       <c r="T50">
-        <v>2.829505079840999</v>
+        <v>2.884985571602588</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-0.7445060181141225</v>
+        <v>-0.7293120177444467</v>
       </c>
       <c r="W50">
-        <v>0.4113545190713101</v>
+        <v>0.4077717737841405</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5512,7 +5523,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-2.97802407245649</v>
+        <v>-2.917248070977787</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5520,22 +5531,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2986511430592712</v>
+        <v>0.3005511430592712</v>
       </c>
       <c r="C51">
-        <v>-2.17130114533483</v>
+        <v>-2.264889576144273</v>
       </c>
       <c r="D51">
-        <v>1.768298854665169</v>
+        <v>1.755110423855726</v>
       </c>
       <c r="E51">
-        <v>3.9396</v>
+        <v>4.02</v>
       </c>
       <c r="F51">
-        <v>3.9396</v>
+        <v>4.02</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5556,37 +5567,37 @@
         <v>-2.71</v>
       </c>
       <c r="M51">
-        <v>0.9289576799999999</v>
+        <v>0.947916</v>
       </c>
       <c r="N51">
-        <v>-3.638957679999999</v>
+        <v>-3.657915999999999</v>
       </c>
       <c r="O51">
-        <v>-0.9097394199999999</v>
+        <v>-0.9144789999999998</v>
       </c>
       <c r="P51">
-        <v>-2.72921826</v>
+        <v>-2.743436999999999</v>
       </c>
       <c r="Q51">
-        <v>2.95078174</v>
+        <v>2.936563</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.193809752754985</v>
+        <v>0.1967699478100847</v>
       </c>
       <c r="T51">
-        <v>2.884985571602588</v>
+        <v>2.94268528303464</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.7293120177444467</v>
+        <v>-0.7147257773895576</v>
       </c>
       <c r="W51">
-        <v>0.4077717737841405</v>
+        <v>0.4043323383084577</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5594,7 +5605,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-2.917248070977787</v>
+        <v>-2.85890310955823</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5602,22 +5613,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.3005511430592712</v>
+        <v>0.3024511430592712</v>
       </c>
       <c r="C52">
-        <v>-2.264889576144273</v>
+        <v>-2.358282737856223</v>
       </c>
       <c r="D52">
-        <v>1.755110423855726</v>
+        <v>1.742117262143776</v>
       </c>
       <c r="E52">
-        <v>4.02</v>
+        <v>4.1004</v>
       </c>
       <c r="F52">
-        <v>4.02</v>
+        <v>4.1004</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5638,37 +5649,37 @@
         <v>-2.71</v>
       </c>
       <c r="M52">
-        <v>0.947916</v>
+        <v>0.96687432</v>
       </c>
       <c r="N52">
-        <v>-3.657915999999999</v>
+        <v>-3.67687432</v>
       </c>
       <c r="O52">
-        <v>-0.9144789999999998</v>
+        <v>-0.9192185799999999</v>
       </c>
       <c r="P52">
-        <v>-2.743436999999999</v>
+        <v>-2.75765574</v>
       </c>
       <c r="Q52">
-        <v>2.936563</v>
+        <v>2.92234426</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1967699478100847</v>
+        <v>0.1998509671531477</v>
       </c>
       <c r="T52">
-        <v>2.94268528303464</v>
+        <v>3.002740084729224</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.7147257773895576</v>
+        <v>-0.7007115464603506</v>
       </c>
       <c r="W52">
-        <v>0.4043323383084577</v>
+        <v>0.4010277826553507</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5676,7 +5687,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-2.85890310955823</v>
+        <v>-2.802846185841402</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5684,22 +5695,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.3024511430592712</v>
+        <v>0.3043511430592712</v>
       </c>
       <c r="C53">
-        <v>-2.358282737856223</v>
+        <v>-2.451484935359231</v>
       </c>
       <c r="D53">
-        <v>1.742117262143776</v>
+        <v>1.729315064640769</v>
       </c>
       <c r="E53">
-        <v>4.1004</v>
+        <v>4.1808</v>
       </c>
       <c r="F53">
-        <v>4.1004</v>
+        <v>4.1808</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5720,37 +5731,37 @@
         <v>-2.71</v>
       </c>
       <c r="M53">
-        <v>0.96687432</v>
+        <v>0.9858326399999999</v>
       </c>
       <c r="N53">
-        <v>-3.67687432</v>
+        <v>-3.695832639999999</v>
       </c>
       <c r="O53">
-        <v>-0.9192185799999999</v>
+        <v>-0.9239581599999999</v>
       </c>
       <c r="P53">
-        <v>-2.75765574</v>
+        <v>-2.77187448</v>
       </c>
       <c r="Q53">
-        <v>2.92234426</v>
+        <v>2.90812552</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1998509671531477</v>
+        <v>0.2030603623021716</v>
       </c>
       <c r="T53">
-        <v>3.002740084729224</v>
+        <v>3.06529716982775</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.7007115464603506</v>
+        <v>-0.6872363244130362</v>
       </c>
       <c r="W53">
-        <v>0.4010277826553507</v>
+        <v>0.3978503252965939</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5758,7 +5769,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-2.802846185841402</v>
+        <v>-2.748945297652145</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5766,22 +5777,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.3043511430592712</v>
+        <v>0.3062511430592713</v>
       </c>
       <c r="C54">
-        <v>-2.451484935359231</v>
+        <v>-2.544500347924611</v>
       </c>
       <c r="D54">
-        <v>1.729315064640769</v>
+        <v>1.716699652075388</v>
       </c>
       <c r="E54">
-        <v>4.1808</v>
+        <v>4.2612</v>
       </c>
       <c r="F54">
-        <v>4.1808</v>
+        <v>4.2612</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5802,37 +5813,37 @@
         <v>-2.71</v>
       </c>
       <c r="M54">
-        <v>0.9858326399999999</v>
+        <v>1.00479096</v>
       </c>
       <c r="N54">
-        <v>-3.695832639999999</v>
+        <v>-3.714790959999999</v>
       </c>
       <c r="O54">
-        <v>-0.9239581599999999</v>
+        <v>-0.9286977399999998</v>
       </c>
       <c r="P54">
-        <v>-2.77187448</v>
+        <v>-2.78609322</v>
       </c>
       <c r="Q54">
-        <v>2.90812552</v>
+        <v>2.89390678</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2030603623021716</v>
+        <v>0.2064063274575369</v>
       </c>
       <c r="T54">
-        <v>3.06529716982775</v>
+        <v>3.130516258547489</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.6872363244130362</v>
+        <v>-0.6742696013109034</v>
       </c>
       <c r="W54">
-        <v>0.3978503252965939</v>
+        <v>0.3947927719891111</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5840,7 +5851,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-2.748945297652145</v>
+        <v>-2.697078405243613</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5848,22 +5859,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.3062511430592713</v>
+        <v>0.3081511430592712</v>
       </c>
       <c r="C55">
-        <v>-2.544500347924611</v>
+        <v>-2.637333033755167</v>
       </c>
       <c r="D55">
-        <v>1.716699652075388</v>
+        <v>1.704266966244833</v>
       </c>
       <c r="E55">
-        <v>4.2612</v>
+        <v>4.3416</v>
       </c>
       <c r="F55">
-        <v>4.2612</v>
+        <v>4.3416</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5884,37 +5895,37 @@
         <v>-2.71</v>
       </c>
       <c r="M55">
-        <v>1.00479096</v>
+        <v>1.02374928</v>
       </c>
       <c r="N55">
-        <v>-3.714790959999999</v>
+        <v>-3.73374928</v>
       </c>
       <c r="O55">
-        <v>-0.9286977399999998</v>
+        <v>-0.9334373199999999</v>
       </c>
       <c r="P55">
-        <v>-2.78609322</v>
+        <v>-2.80031196</v>
       </c>
       <c r="Q55">
-        <v>2.89390678</v>
+        <v>2.87968804</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2064063274575369</v>
+        <v>0.2098977693587877</v>
       </c>
       <c r="T55">
-        <v>3.130516258547489</v>
+        <v>3.198570959820261</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.6742696013109034</v>
+        <v>-0.6617831272125534</v>
       </c>
       <c r="W55">
-        <v>0.3947927719891111</v>
+        <v>0.3918484613967201</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5922,7 +5933,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-2.697078405243613</v>
+        <v>-2.647132508850214</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5930,22 +5941,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.3081511430592712</v>
+        <v>0.3100511430592712</v>
       </c>
       <c r="C56">
-        <v>-2.637333033755167</v>
+        <v>-2.729986934337686</v>
       </c>
       <c r="D56">
-        <v>1.704266966244833</v>
+        <v>1.692013065662314</v>
       </c>
       <c r="E56">
-        <v>4.3416</v>
+        <v>4.422</v>
       </c>
       <c r="F56">
-        <v>4.3416</v>
+        <v>4.422</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5966,37 +5977,37 @@
         <v>-2.71</v>
       </c>
       <c r="M56">
-        <v>1.02374928</v>
+        <v>1.0427076</v>
       </c>
       <c r="N56">
-        <v>-3.73374928</v>
+        <v>-3.752707599999999</v>
       </c>
       <c r="O56">
-        <v>-0.9334373199999999</v>
+        <v>-0.9381768999999999</v>
       </c>
       <c r="P56">
-        <v>-2.80031196</v>
+        <v>-2.8145307</v>
       </c>
       <c r="Q56">
-        <v>2.87968804</v>
+        <v>2.8654693</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2098977693587877</v>
+        <v>0.2135443864556497</v>
       </c>
       <c r="T56">
-        <v>3.198570959820261</v>
+        <v>3.269650314482933</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.6617831272125534</v>
+        <v>-0.6497507067177797</v>
       </c>
       <c r="W56">
-        <v>0.3918484613967201</v>
+        <v>0.3890112166440525</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6004,7 +6015,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-2.647132508850214</v>
+        <v>-2.599002826871119</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6012,22 +6023,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.3100511430592712</v>
+        <v>0.3119511430592712</v>
       </c>
       <c r="C57">
-        <v>-2.729986934337686</v>
+        <v>-2.822465878608995</v>
       </c>
       <c r="D57">
-        <v>1.692013065662314</v>
+        <v>1.679934121391005</v>
       </c>
       <c r="E57">
-        <v>4.422</v>
+        <v>4.5024</v>
       </c>
       <c r="F57">
-        <v>4.422</v>
+        <v>4.5024</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -6048,37 +6059,37 @@
         <v>-2.71</v>
       </c>
       <c r="M57">
-        <v>1.0427076</v>
+        <v>1.06166592</v>
       </c>
       <c r="N57">
-        <v>-3.752707599999999</v>
+        <v>-3.771665919999999</v>
       </c>
       <c r="O57">
-        <v>-0.9381768999999999</v>
+        <v>-0.9429164799999998</v>
       </c>
       <c r="P57">
-        <v>-2.8145307</v>
+        <v>-2.828749439999999</v>
       </c>
       <c r="Q57">
-        <v>2.8654693</v>
+        <v>2.85125056</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2135443864556497</v>
+        <v>0.2173567588750962</v>
       </c>
       <c r="T57">
-        <v>3.269650314482933</v>
+        <v>3.343960548903</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.6497507067177797</v>
+        <v>-0.6381480155263907</v>
       </c>
       <c r="W57">
-        <v>0.3890112166440525</v>
+        <v>0.3862753020611229</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6086,7 +6097,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-2.599002826871119</v>
+        <v>-2.552592062105563</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6094,22 +6105,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.3119511430592712</v>
+        <v>0.3138511430592713</v>
       </c>
       <c r="C58">
-        <v>-2.822465878608995</v>
+        <v>-2.914773586944853</v>
       </c>
       <c r="D58">
-        <v>1.679934121391005</v>
+        <v>1.668026413055146</v>
       </c>
       <c r="E58">
-        <v>4.5024</v>
+        <v>4.5828</v>
       </c>
       <c r="F58">
-        <v>4.5024</v>
+        <v>4.5828</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6130,37 +6141,37 @@
         <v>-2.71</v>
       </c>
       <c r="M58">
-        <v>1.06166592</v>
+        <v>1.08062424</v>
       </c>
       <c r="N58">
-        <v>-3.771665919999999</v>
+        <v>-3.79062424</v>
       </c>
       <c r="O58">
-        <v>-0.9429164799999998</v>
+        <v>-0.9476560599999999</v>
       </c>
       <c r="P58">
-        <v>-2.828749439999999</v>
+        <v>-2.84296818</v>
       </c>
       <c r="Q58">
-        <v>2.85125056</v>
+        <v>2.83703182</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2173567588750962</v>
+        <v>0.221346450941959</v>
       </c>
       <c r="T58">
-        <v>3.343960548903</v>
+        <v>3.421727073296093</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.6381480155263907</v>
+        <v>-0.6269524363066296</v>
       </c>
       <c r="W58">
-        <v>0.3862753020611229</v>
+        <v>0.3836353844811033</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6168,7 +6179,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-2.552592062105563</v>
+        <v>-2.507809745226518</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6176,22 +6187,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.3138511430592713</v>
+        <v>0.3157511430592712</v>
       </c>
       <c r="C59">
-        <v>-2.914773586944853</v>
+        <v>-3.006913674980372</v>
       </c>
       <c r="D59">
-        <v>1.668026413055146</v>
+        <v>1.656286325019628</v>
       </c>
       <c r="E59">
-        <v>4.5828</v>
+        <v>4.6632</v>
       </c>
       <c r="F59">
-        <v>4.5828</v>
+        <v>4.6632</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6212,37 +6223,37 @@
         <v>-2.71</v>
       </c>
       <c r="M59">
-        <v>1.08062424</v>
+        <v>1.09958256</v>
       </c>
       <c r="N59">
-        <v>-3.79062424</v>
+        <v>-3.80958256</v>
       </c>
       <c r="O59">
-        <v>-0.9476560599999999</v>
+        <v>-0.9523956399999999</v>
       </c>
       <c r="P59">
-        <v>-2.84296818</v>
+        <v>-2.85718692</v>
       </c>
       <c r="Q59">
-        <v>2.83703182</v>
+        <v>2.82281308</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.221346450941959</v>
+        <v>0.2255261283453389</v>
       </c>
       <c r="T59">
-        <v>3.421727073296093</v>
+        <v>3.503196765517429</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.6269524363066296</v>
+        <v>-0.616142911542722</v>
       </c>
       <c r="W59">
-        <v>0.3836353844811033</v>
+        <v>0.3810864985417739</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6250,7 +6261,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-2.507809745226518</v>
+        <v>-2.464571646170888</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6258,22 +6269,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.3157511430592712</v>
+        <v>0.3176511430592712</v>
       </c>
       <c r="C60">
-        <v>-3.006913674980371</v>
+        <v>-3.098889657270249</v>
       </c>
       <c r="D60">
-        <v>1.656286325019628</v>
+        <v>1.64471034272975</v>
       </c>
       <c r="E60">
-        <v>4.663199999999999</v>
+        <v>4.743599999999999</v>
       </c>
       <c r="F60">
-        <v>4.663199999999999</v>
+        <v>4.743599999999999</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6294,37 +6305,37 @@
         <v>-2.71</v>
       </c>
       <c r="M60">
-        <v>1.09958256</v>
+        <v>1.11854088</v>
       </c>
       <c r="N60">
-        <v>-3.809582559999999</v>
+        <v>-3.828540879999999</v>
       </c>
       <c r="O60">
-        <v>-0.9523956399999998</v>
+        <v>-0.9571352199999998</v>
       </c>
       <c r="P60">
-        <v>-2.857186919999999</v>
+        <v>-2.87140566</v>
       </c>
       <c r="Q60">
-        <v>2.82281308</v>
+        <v>2.80859434</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2255261283453389</v>
+        <v>0.2299096924513228</v>
       </c>
       <c r="T60">
-        <v>3.503196765517428</v>
+        <v>3.588640589066634</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.6161429115427222</v>
+        <v>-0.6056998113470828</v>
       </c>
       <c r="W60">
-        <v>0.3810864985417739</v>
+        <v>0.3786240155156422</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6332,7 +6343,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-2.464571646170889</v>
+        <v>-2.422799245388331</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6340,22 +6351,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.3176511430592712</v>
+        <v>0.3195511430592712</v>
       </c>
       <c r="C61">
-        <v>-3.098889657270249</v>
+        <v>-3.190704950796567</v>
       </c>
       <c r="D61">
-        <v>1.64471034272975</v>
+        <v>1.633295049203432</v>
       </c>
       <c r="E61">
-        <v>4.743599999999999</v>
+        <v>4.823999999999999</v>
       </c>
       <c r="F61">
-        <v>4.743599999999999</v>
+        <v>4.823999999999999</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6376,37 +6387,37 @@
         <v>-2.71</v>
       </c>
       <c r="M61">
-        <v>1.11854088</v>
+        <v>1.1374992</v>
       </c>
       <c r="N61">
-        <v>-3.828540879999999</v>
+        <v>-3.847499199999999</v>
       </c>
       <c r="O61">
-        <v>-0.9571352199999998</v>
+        <v>-0.9618747999999998</v>
       </c>
       <c r="P61">
-        <v>-2.87140566</v>
+        <v>-2.885624399999999</v>
       </c>
       <c r="Q61">
-        <v>2.80859434</v>
+        <v>2.7943756</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2299096924513228</v>
+        <v>0.2345124347626058</v>
       </c>
       <c r="T61">
-        <v>3.588640589066634</v>
+        <v>3.678356603793299</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.6056998113470828</v>
+        <v>-0.5956048144912981</v>
       </c>
       <c r="W61">
-        <v>0.3786240155156422</v>
+        <v>0.3762436152570481</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6414,7 +6425,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-2.422799245388331</v>
+        <v>-2.382419257965192</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6422,22 +6433,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.3195511430592712</v>
+        <v>0.3214511430592712</v>
       </c>
       <c r="C62">
-        <v>-3.190704950796567</v>
+        <v>-3.282362878331513</v>
       </c>
       <c r="D62">
-        <v>1.633295049203432</v>
+        <v>1.622037121668486</v>
       </c>
       <c r="E62">
-        <v>4.823999999999999</v>
+        <v>4.904399999999999</v>
       </c>
       <c r="F62">
-        <v>4.823999999999999</v>
+        <v>4.904399999999999</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6458,37 +6469,37 @@
         <v>-2.71</v>
       </c>
       <c r="M62">
-        <v>1.1374992</v>
+        <v>1.15645752</v>
       </c>
       <c r="N62">
-        <v>-3.847499199999999</v>
+        <v>-3.866457519999999</v>
       </c>
       <c r="O62">
-        <v>-0.9618747999999998</v>
+        <v>-0.9666143799999998</v>
       </c>
       <c r="P62">
-        <v>-2.885624399999999</v>
+        <v>-2.899843139999999</v>
       </c>
       <c r="Q62">
-        <v>2.7943756</v>
+        <v>2.78015686</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2345124347626058</v>
+        <v>0.2393512151411342</v>
       </c>
       <c r="T62">
-        <v>3.678356603793299</v>
+        <v>3.772673439788</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.5956048144912981</v>
+        <v>-0.5858408011389817</v>
       </c>
       <c r="W62">
-        <v>0.3762436152570481</v>
+        <v>0.3739412609085719</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6496,7 +6507,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-2.382419257965192</v>
+        <v>-2.343363204555927</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6504,22 +6515,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.3214511430592712</v>
+        <v>0.3233511430592712</v>
       </c>
       <c r="C63">
-        <v>-3.282362878331513</v>
+        <v>-3.373866671661998</v>
       </c>
       <c r="D63">
-        <v>1.622037121668486</v>
+        <v>1.610933328338001</v>
       </c>
       <c r="E63">
-        <v>4.904399999999999</v>
+        <v>4.984799999999999</v>
       </c>
       <c r="F63">
-        <v>4.904399999999999</v>
+        <v>4.984799999999999</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6540,37 +6551,37 @@
         <v>-2.71</v>
       </c>
       <c r="M63">
-        <v>1.15645752</v>
+        <v>1.17541584</v>
       </c>
       <c r="N63">
-        <v>-3.866457519999999</v>
+        <v>-3.885415839999999</v>
       </c>
       <c r="O63">
-        <v>-0.9666143799999998</v>
+        <v>-0.9713539599999998</v>
       </c>
       <c r="P63">
-        <v>-2.899843139999999</v>
+        <v>-2.914061879999999</v>
       </c>
       <c r="Q63">
-        <v>2.78015686</v>
+        <v>2.76593812</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2393512151411342</v>
+        <v>0.244444668171164</v>
       </c>
       <c r="T63">
-        <v>3.772673439788</v>
+        <v>3.87195431978242</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.5858408011389817</v>
+        <v>-0.5763917559593207</v>
       </c>
       <c r="W63">
-        <v>0.3739412609085719</v>
+        <v>0.3717131760552078</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6578,7 +6589,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-2.343363204555927</v>
+        <v>-2.305567023837283</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6586,22 +6597,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.3233511430592712</v>
+        <v>0.3252511430592712</v>
       </c>
       <c r="C64">
-        <v>-3.373866671661998</v>
+        <v>-3.465219474682716</v>
       </c>
       <c r="D64">
-        <v>1.610933328338001</v>
+        <v>1.599980525317285</v>
       </c>
       <c r="E64">
-        <v>4.984799999999999</v>
+        <v>5.0652</v>
       </c>
       <c r="F64">
-        <v>4.984799999999999</v>
+        <v>5.0652</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6622,37 +6633,37 @@
         <v>-2.71</v>
       </c>
       <c r="M64">
-        <v>1.17541584</v>
+        <v>1.19437416</v>
       </c>
       <c r="N64">
-        <v>-3.885415839999999</v>
+        <v>-3.90437416</v>
       </c>
       <c r="O64">
-        <v>-0.9713539599999998</v>
+        <v>-0.9760935399999999</v>
       </c>
       <c r="P64">
-        <v>-2.914061879999999</v>
+        <v>-2.92828062</v>
       </c>
       <c r="Q64">
-        <v>2.76593812</v>
+        <v>2.75171938</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.244444668171164</v>
+        <v>0.2498134429866009</v>
       </c>
       <c r="T64">
-        <v>3.87195431978242</v>
+        <v>3.976601733830594</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.5763917559593207</v>
+        <v>-0.5672426804679028</v>
       </c>
       <c r="W64">
-        <v>0.3717131760552078</v>
+        <v>0.3695558240543315</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6660,7 +6671,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-2.305567023837283</v>
+        <v>-2.268970721871612</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6668,22 +6679,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3252511430592712</v>
+        <v>0.3271511430592712</v>
       </c>
       <c r="C65">
-        <v>-3.465219474682716</v>
+        <v>-3.556424346363875</v>
       </c>
       <c r="D65">
-        <v>1.599980525317285</v>
+        <v>1.589175653636125</v>
       </c>
       <c r="E65">
-        <v>5.0652</v>
+        <v>5.1456</v>
       </c>
       <c r="F65">
-        <v>5.0652</v>
+        <v>5.1456</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6704,37 +6715,37 @@
         <v>-2.71</v>
       </c>
       <c r="M65">
-        <v>1.19437416</v>
+        <v>1.21333248</v>
       </c>
       <c r="N65">
-        <v>-3.90437416</v>
+        <v>-3.92333248</v>
       </c>
       <c r="O65">
-        <v>-0.9760935399999999</v>
+        <v>-0.9808331199999999</v>
       </c>
       <c r="P65">
-        <v>-2.92828062</v>
+        <v>-2.94249936</v>
       </c>
       <c r="Q65">
-        <v>2.75171938</v>
+        <v>2.73750064</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2498134429866009</v>
+        <v>0.2554804830695621</v>
       </c>
       <c r="T65">
-        <v>3.976601733830594</v>
+        <v>4.087062893103666</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.5672426804679028</v>
+        <v>-0.5583795135855919</v>
       </c>
       <c r="W65">
-        <v>0.3695558240543315</v>
+        <v>0.3674658893034826</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6742,7 +6753,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-2.268970721871612</v>
+        <v>-2.233518054342368</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6750,22 +6761,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3271511430592712</v>
+        <v>0.3290511430592712</v>
       </c>
       <c r="C66">
-        <v>-3.556424346363875</v>
+        <v>-3.647484263599503</v>
       </c>
       <c r="D66">
-        <v>1.589175653636125</v>
+        <v>1.578515736400497</v>
       </c>
       <c r="E66">
-        <v>5.1456</v>
+        <v>5.226</v>
       </c>
       <c r="F66">
-        <v>5.1456</v>
+        <v>5.226</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6786,37 +6797,37 @@
         <v>-2.71</v>
       </c>
       <c r="M66">
-        <v>1.21333248</v>
+        <v>1.2322908</v>
       </c>
       <c r="N66">
-        <v>-3.92333248</v>
+        <v>-3.942290799999999</v>
       </c>
       <c r="O66">
-        <v>-0.9808331199999999</v>
+        <v>-0.9855726999999999</v>
       </c>
       <c r="P66">
-        <v>-2.94249936</v>
+        <v>-2.9567181</v>
       </c>
       <c r="Q66">
-        <v>2.73750064</v>
+        <v>2.7232819</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2554804830695621</v>
+        <v>0.2614713540144067</v>
       </c>
       <c r="T66">
-        <v>4.087062893103666</v>
+        <v>4.203836118620914</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.5583795135855919</v>
+        <v>-0.5497890595304289</v>
       </c>
       <c r="W66">
-        <v>0.3674658893034826</v>
+        <v>0.3654402602372752</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6824,7 +6835,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-2.233518054342368</v>
+        <v>-2.199156238121715</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6832,22 +6843,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.3290511430592712</v>
+        <v>0.3309511430592712</v>
       </c>
       <c r="C67">
-        <v>-3.647484263599503</v>
+        <v>-3.73840212394186</v>
       </c>
       <c r="D67">
-        <v>1.578515736400497</v>
+        <v>1.56799787605814</v>
       </c>
       <c r="E67">
-        <v>5.226</v>
+        <v>5.3064</v>
       </c>
       <c r="F67">
-        <v>5.226</v>
+        <v>5.3064</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6868,37 +6879,37 @@
         <v>-2.71</v>
       </c>
       <c r="M67">
-        <v>1.2322908</v>
+        <v>1.25124912</v>
       </c>
       <c r="N67">
-        <v>-3.942290799999999</v>
+        <v>-3.96124912</v>
       </c>
       <c r="O67">
-        <v>-0.9855726999999999</v>
+        <v>-0.9903122799999999</v>
       </c>
       <c r="P67">
-        <v>-2.9567181</v>
+        <v>-2.97093684</v>
       </c>
       <c r="Q67">
-        <v>2.7232819</v>
+        <v>2.70906316</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2614713540144067</v>
+        <v>0.2678146291324775</v>
       </c>
       <c r="T67">
-        <v>4.203836118620914</v>
+        <v>4.327478357403883</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.5497890595304289</v>
+        <v>-0.5414589222648164</v>
       </c>
       <c r="W67">
-        <v>0.3654402602372752</v>
+        <v>0.3634760138700437</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6906,7 +6917,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-2.199156238121715</v>
+        <v>-2.165835689059266</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6914,22 +6925,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.3309511430592712</v>
+        <v>0.3328511430592712</v>
       </c>
       <c r="C68">
-        <v>-3.73840212394186</v>
+        <v>-3.829180748227273</v>
       </c>
       <c r="D68">
-        <v>1.56799787605814</v>
+        <v>1.557619251772727</v>
       </c>
       <c r="E68">
-        <v>5.3064</v>
+        <v>5.3868</v>
       </c>
       <c r="F68">
-        <v>5.3064</v>
+        <v>5.3868</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6950,37 +6961,37 @@
         <v>-2.71</v>
       </c>
       <c r="M68">
-        <v>1.25124912</v>
+        <v>1.27020744</v>
       </c>
       <c r="N68">
-        <v>-3.96124912</v>
+        <v>-3.98020744</v>
       </c>
       <c r="O68">
-        <v>-0.9903122799999999</v>
+        <v>-0.9950518599999999</v>
       </c>
       <c r="P68">
-        <v>-2.97093684</v>
+        <v>-2.98515558</v>
       </c>
       <c r="Q68">
-        <v>2.70906316</v>
+        <v>2.69484442</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2678146291324775</v>
+        <v>0.2745423451667949</v>
       </c>
       <c r="T68">
-        <v>4.327478357403883</v>
+        <v>4.458614065203999</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.5414589222648164</v>
+        <v>-0.5333774458131026</v>
       </c>
       <c r="W68">
-        <v>0.3634760138700437</v>
+        <v>0.3615704017227296</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6988,7 +6999,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-2.165835689059266</v>
+        <v>-2.133509783252411</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6996,22 +7007,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3328511430592712</v>
+        <v>0.3347511430592712</v>
       </c>
       <c r="C69">
-        <v>-3.829180748227273</v>
+        <v>-3.919822883098361</v>
       </c>
       <c r="D69">
-        <v>1.557619251772727</v>
+        <v>1.547377116901639</v>
       </c>
       <c r="E69">
-        <v>5.3868</v>
+        <v>5.4672</v>
       </c>
       <c r="F69">
-        <v>5.3868</v>
+        <v>5.4672</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -7032,37 +7043,37 @@
         <v>-2.71</v>
       </c>
       <c r="M69">
-        <v>1.27020744</v>
+        <v>1.28916576</v>
       </c>
       <c r="N69">
-        <v>-3.98020744</v>
+        <v>-3.999165759999999</v>
       </c>
       <c r="O69">
-        <v>-0.9950518599999999</v>
+        <v>-0.9997914399999999</v>
       </c>
       <c r="P69">
-        <v>-2.98515558</v>
+        <v>-2.999374319999999</v>
       </c>
       <c r="Q69">
-        <v>2.69484442</v>
+        <v>2.68062568</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2745423451667949</v>
+        <v>0.2816905434532573</v>
       </c>
       <c r="T69">
-        <v>4.458614065203999</v>
+        <v>4.597945754741625</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.5333774458131026</v>
+        <v>-0.5255336598452629</v>
       </c>
       <c r="W69">
-        <v>0.3615704017227296</v>
+        <v>0.359720836991513</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7070,7 +7081,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-2.133509783252411</v>
+        <v>-2.102134639381051</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7078,22 +7089,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3347511430592712</v>
+        <v>0.3366511430592712</v>
       </c>
       <c r="C70">
-        <v>-3.919822883098361</v>
+        <v>-4.01033120342741</v>
       </c>
       <c r="D70">
-        <v>1.547377116901639</v>
+        <v>1.53726879657259</v>
       </c>
       <c r="E70">
-        <v>5.4672</v>
+        <v>5.5476</v>
       </c>
       <c r="F70">
-        <v>5.4672</v>
+        <v>5.5476</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7114,37 +7125,37 @@
         <v>-2.71</v>
       </c>
       <c r="M70">
-        <v>1.28916576</v>
+        <v>1.30812408</v>
       </c>
       <c r="N70">
-        <v>-3.999165759999999</v>
+        <v>-4.01812408</v>
       </c>
       <c r="O70">
-        <v>-0.9997914399999999</v>
+        <v>-1.00453102</v>
       </c>
       <c r="P70">
-        <v>-2.999374319999999</v>
+        <v>-3.01359306</v>
       </c>
       <c r="Q70">
-        <v>2.68062568</v>
+        <v>2.66640694</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2816905434532573</v>
+        <v>0.2892999158227173</v>
       </c>
       <c r="T70">
-        <v>4.597945754741625</v>
+        <v>4.746266585539743</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.5255336598452629</v>
+        <v>-0.5179172299924331</v>
       </c>
       <c r="W70">
-        <v>0.359720836991513</v>
+        <v>0.3579248828322157</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7152,7 +7163,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-2.102134639381051</v>
+        <v>-2.071668919969732</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7160,22 +7171,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3366511430592712</v>
+        <v>0.3385511430592713</v>
       </c>
       <c r="C71">
-        <v>-4.01033120342741</v>
+        <v>-4.100708314645372</v>
       </c>
       <c r="D71">
-        <v>1.53726879657259</v>
+        <v>1.527291685354628</v>
       </c>
       <c r="E71">
-        <v>5.5476</v>
+        <v>5.628</v>
       </c>
       <c r="F71">
-        <v>5.5476</v>
+        <v>5.628</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7196,37 +7207,37 @@
         <v>-2.71</v>
       </c>
       <c r="M71">
-        <v>1.30812408</v>
+        <v>1.3270824</v>
       </c>
       <c r="N71">
-        <v>-4.01812408</v>
+        <v>-4.037082399999999</v>
       </c>
       <c r="O71">
-        <v>-1.00453102</v>
+        <v>-1.0092706</v>
       </c>
       <c r="P71">
-        <v>-3.01359306</v>
+        <v>-3.027811799999999</v>
       </c>
       <c r="Q71">
-        <v>2.66640694</v>
+        <v>2.6521882</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2892999158227173</v>
+        <v>0.2974165796834745</v>
       </c>
       <c r="T71">
-        <v>4.746266585539743</v>
+        <v>4.904475471724401</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.5179172299924331</v>
+        <v>-0.5105184124211125</v>
       </c>
       <c r="W71">
-        <v>0.3579248828322157</v>
+        <v>0.3561802416488984</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7234,7 +7245,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-2.071668919969732</v>
+        <v>-2.04207364968445</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7242,22 +7253,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3385511430592713</v>
+        <v>0.3404511430592712</v>
       </c>
       <c r="C72">
-        <v>-4.100708314645372</v>
+        <v>-4.190956754980762</v>
       </c>
       <c r="D72">
-        <v>1.527291685354628</v>
+        <v>1.517443245019238</v>
       </c>
       <c r="E72">
-        <v>5.628</v>
+        <v>5.7084</v>
       </c>
       <c r="F72">
-        <v>5.628</v>
+        <v>5.7084</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7278,37 +7289,37 @@
         <v>-2.71</v>
       </c>
       <c r="M72">
-        <v>1.3270824</v>
+        <v>1.34604072</v>
       </c>
       <c r="N72">
-        <v>-4.037082399999999</v>
+        <v>-4.056040719999999</v>
       </c>
       <c r="O72">
-        <v>-1.0092706</v>
+        <v>-1.01401018</v>
       </c>
       <c r="P72">
-        <v>-3.027811799999999</v>
+        <v>-3.04203054</v>
       </c>
       <c r="Q72">
-        <v>2.6521882</v>
+        <v>2.63796946</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2974165796834745</v>
+        <v>0.3060930134656633</v>
       </c>
       <c r="T72">
-        <v>4.904475471724401</v>
+        <v>5.073595315576966</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.5105184124211125</v>
+        <v>-0.5033280122461673</v>
       </c>
       <c r="W72">
-        <v>0.3561802416488984</v>
+        <v>0.3544847452876463</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7316,7 +7327,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-2.04207364968445</v>
+        <v>-2.013312048984669</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7324,22 +7335,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3404511430592712</v>
+        <v>0.3423511430592712</v>
       </c>
       <c r="C73">
-        <v>-4.190956754980761</v>
+        <v>-4.281078997612482</v>
       </c>
       <c r="D73">
-        <v>1.517443245019238</v>
+        <v>1.507721002387516</v>
       </c>
       <c r="E73">
-        <v>5.708399999999999</v>
+        <v>5.788799999999999</v>
       </c>
       <c r="F73">
-        <v>5.708399999999999</v>
+        <v>5.788799999999999</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7360,37 +7371,37 @@
         <v>-2.71</v>
       </c>
       <c r="M73">
-        <v>1.34604072</v>
+        <v>1.36499904</v>
       </c>
       <c r="N73">
-        <v>-4.056040719999999</v>
+        <v>-4.07499904</v>
       </c>
       <c r="O73">
-        <v>-1.01401018</v>
+        <v>-1.01874976</v>
       </c>
       <c r="P73">
-        <v>-3.04203054</v>
+        <v>-3.05624928</v>
       </c>
       <c r="Q73">
-        <v>2.63796946</v>
+        <v>2.62375072</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3060930134656633</v>
+        <v>0.3153891925180083</v>
       </c>
       <c r="T73">
-        <v>5.073595315576965</v>
+        <v>5.254795148276142</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.5033280122461673</v>
+        <v>-0.496337345409415</v>
       </c>
       <c r="W73">
-        <v>0.3544847452876463</v>
+        <v>0.3528363460475401</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7398,7 +7409,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-2.013312048984669</v>
+        <v>-1.98534938163766</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7406,22 +7417,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3423511430592712</v>
+        <v>0.3442511430592712</v>
       </c>
       <c r="C74">
-        <v>-4.281078997612482</v>
+        <v>-4.371077452740421</v>
       </c>
       <c r="D74">
-        <v>1.507721002387516</v>
+        <v>1.498122547259579</v>
       </c>
       <c r="E74">
-        <v>5.788799999999999</v>
+        <v>5.869199999999999</v>
       </c>
       <c r="F74">
-        <v>5.788799999999999</v>
+        <v>5.869199999999999</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7442,37 +7453,37 @@
         <v>-2.71</v>
       </c>
       <c r="M74">
-        <v>1.36499904</v>
+        <v>1.38395736</v>
       </c>
       <c r="N74">
-        <v>-4.07499904</v>
+        <v>-4.093957359999999</v>
       </c>
       <c r="O74">
-        <v>-1.01874976</v>
+        <v>-1.02348934</v>
       </c>
       <c r="P74">
-        <v>-3.05624928</v>
+        <v>-3.070468019999999</v>
       </c>
       <c r="Q74">
-        <v>2.62375072</v>
+        <v>2.60953198</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3153891925180083</v>
+        <v>0.3253739774260827</v>
       </c>
       <c r="T74">
-        <v>5.254795148276142</v>
+        <v>5.449417190804888</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.496337345409415</v>
+        <v>-0.4895382036914778</v>
       </c>
       <c r="W74">
-        <v>0.3528363460475401</v>
+        <v>0.3512331084304505</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7480,7 +7491,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-1.98534938163766</v>
+        <v>-1.958152814765911</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7488,22 +7499,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3442511430592712</v>
+        <v>0.3461511430592712</v>
       </c>
       <c r="C75">
-        <v>-4.371077452740421</v>
+        <v>-4.460954469577448</v>
       </c>
       <c r="D75">
-        <v>1.498122547259579</v>
+        <v>1.488645530422551</v>
       </c>
       <c r="E75">
-        <v>5.869199999999999</v>
+        <v>5.949599999999999</v>
       </c>
       <c r="F75">
-        <v>5.869199999999999</v>
+        <v>5.949599999999999</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7524,37 +7535,37 @@
         <v>-2.71</v>
       </c>
       <c r="M75">
-        <v>1.38395736</v>
+        <v>1.40291568</v>
       </c>
       <c r="N75">
-        <v>-4.093957359999999</v>
+        <v>-4.11291568</v>
       </c>
       <c r="O75">
-        <v>-1.02348934</v>
+        <v>-1.02822892</v>
       </c>
       <c r="P75">
-        <v>-3.070468019999999</v>
+        <v>-3.084686759999999</v>
       </c>
       <c r="Q75">
-        <v>2.60953198</v>
+        <v>2.59531324</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3253739774260827</v>
+        <v>0.3361268227117013</v>
       </c>
       <c r="T75">
-        <v>5.449417190804888</v>
+        <v>5.659010159681999</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.4895382036914778</v>
+        <v>-0.4829228225605119</v>
       </c>
       <c r="W75">
-        <v>0.3512331084304505</v>
+        <v>0.3496732015597687</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7562,7 +7573,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-1.958152814765911</v>
+        <v>-1.931691290242048</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7570,22 +7581,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3461511430592712</v>
+        <v>0.3480511430592712</v>
       </c>
       <c r="C76">
-        <v>-4.460954469577448</v>
+        <v>-4.550712338266297</v>
       </c>
       <c r="D76">
-        <v>1.488645530422551</v>
+        <v>1.479287661733703</v>
       </c>
       <c r="E76">
-        <v>5.949599999999999</v>
+        <v>6.029999999999999</v>
       </c>
       <c r="F76">
-        <v>5.949599999999999</v>
+        <v>6.029999999999999</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7606,37 +7617,37 @@
         <v>-2.71</v>
       </c>
       <c r="M76">
-        <v>1.40291568</v>
+        <v>1.421874</v>
       </c>
       <c r="N76">
-        <v>-4.11291568</v>
+        <v>-4.131874</v>
       </c>
       <c r="O76">
-        <v>-1.02822892</v>
+        <v>-1.0329685</v>
       </c>
       <c r="P76">
-        <v>-3.084686759999999</v>
+        <v>-3.0989055</v>
       </c>
       <c r="Q76">
-        <v>2.59531324</v>
+        <v>2.5810945</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3361268227117013</v>
+        <v>0.3477398956201694</v>
       </c>
       <c r="T76">
-        <v>5.659010159681999</v>
+        <v>5.885370566069279</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.4829228225605119</v>
+        <v>-0.4764838515930385</v>
       </c>
       <c r="W76">
-        <v>0.3496732015597687</v>
+        <v>0.3481548922056385</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7644,7 +7655,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-1.931691290242048</v>
+        <v>-1.905935406372154</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7652,22 +7663,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3480511430592712</v>
+        <v>0.3499511430592712</v>
       </c>
       <c r="C77">
-        <v>-4.550712338266297</v>
+        <v>-4.640353291724579</v>
       </c>
       <c r="D77">
-        <v>1.479287661733703</v>
+        <v>1.47004670827542</v>
       </c>
       <c r="E77">
-        <v>6.029999999999999</v>
+        <v>6.110399999999999</v>
       </c>
       <c r="F77">
-        <v>6.029999999999999</v>
+        <v>6.110399999999999</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7688,37 +7699,37 @@
         <v>-2.71</v>
       </c>
       <c r="M77">
-        <v>1.421874</v>
+        <v>1.44083232</v>
       </c>
       <c r="N77">
-        <v>-4.131874</v>
+        <v>-4.150832319999999</v>
       </c>
       <c r="O77">
-        <v>-1.0329685</v>
+        <v>-1.03770808</v>
       </c>
       <c r="P77">
-        <v>-3.0989055</v>
+        <v>-3.113124239999999</v>
       </c>
       <c r="Q77">
-        <v>2.5810945</v>
+        <v>2.56687576</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3477398956201694</v>
+        <v>0.3603207246043431</v>
       </c>
       <c r="T77">
-        <v>5.885370566069279</v>
+        <v>6.1305943396555</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.4764838515930385</v>
+        <v>-0.4702143272299721</v>
       </c>
       <c r="W77">
-        <v>0.3481548922056385</v>
+        <v>0.3466765383608275</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7726,7 +7737,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-1.905935406372154</v>
+        <v>-1.880857308919888</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7734,22 +7745,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3499511430592712</v>
+        <v>0.3518511430592712</v>
       </c>
       <c r="C78">
-        <v>-4.640353291724579</v>
+        <v>-4.729879507421091</v>
       </c>
       <c r="D78">
-        <v>1.47004670827542</v>
+        <v>1.460920492578908</v>
       </c>
       <c r="E78">
-        <v>6.110399999999999</v>
+        <v>6.190799999999999</v>
       </c>
       <c r="F78">
-        <v>6.110399999999999</v>
+        <v>6.190799999999999</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7770,37 +7781,37 @@
         <v>-2.71</v>
       </c>
       <c r="M78">
-        <v>1.44083232</v>
+        <v>1.45979064</v>
       </c>
       <c r="N78">
-        <v>-4.150832319999999</v>
+        <v>-4.16979064</v>
       </c>
       <c r="O78">
-        <v>-1.03770808</v>
+        <v>-1.04244766</v>
       </c>
       <c r="P78">
-        <v>-3.113124239999999</v>
+        <v>-3.12734298</v>
       </c>
       <c r="Q78">
-        <v>2.56687576</v>
+        <v>2.55265702</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3603207246043431</v>
+        <v>0.3739955387175754</v>
       </c>
       <c r="T78">
-        <v>6.1305943396555</v>
+        <v>6.397141919640521</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.4702143272299721</v>
+        <v>-0.4641076476555569</v>
       </c>
       <c r="W78">
-        <v>0.3466765383608275</v>
+        <v>0.3452365833171804</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7808,7 +7819,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-1.880857308919888</v>
+        <v>-1.856430590622228</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7816,22 +7827,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3518511430592712</v>
+        <v>0.3537511430592712</v>
       </c>
       <c r="C79">
-        <v>-4.729879507421091</v>
+        <v>-4.819293109086359</v>
       </c>
       <c r="D79">
-        <v>1.460920492578908</v>
+        <v>1.451906890913641</v>
       </c>
       <c r="E79">
-        <v>6.190799999999999</v>
+        <v>6.271199999999999</v>
       </c>
       <c r="F79">
-        <v>6.190799999999999</v>
+        <v>6.271199999999999</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7852,37 +7863,37 @@
         <v>-2.71</v>
       </c>
       <c r="M79">
-        <v>1.45979064</v>
+        <v>1.47874896</v>
       </c>
       <c r="N79">
-        <v>-4.16979064</v>
+        <v>-4.18874896</v>
       </c>
       <c r="O79">
-        <v>-1.04244766</v>
+        <v>-1.04718724</v>
       </c>
       <c r="P79">
-        <v>-3.12734298</v>
+        <v>-3.14156172</v>
       </c>
       <c r="Q79">
-        <v>2.55265702</v>
+        <v>2.53843828</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3739955387175754</v>
+        <v>0.3889135177501926</v>
       </c>
       <c r="T79">
-        <v>6.397141919640521</v>
+        <v>6.687921097806001</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.4641076476555569</v>
+        <v>-0.4581575496086908</v>
       </c>
       <c r="W79">
-        <v>0.3452365833171804</v>
+        <v>0.3438335501977293</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7890,7 +7901,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-1.856430590622228</v>
+        <v>-1.832630198434764</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7898,22 +7909,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3537511430592712</v>
+        <v>0.3556511430592712</v>
       </c>
       <c r="C80">
-        <v>-4.819293109086359</v>
+        <v>-4.908596168360238</v>
       </c>
       <c r="D80">
-        <v>1.451906890913641</v>
+        <v>1.443003831639762</v>
       </c>
       <c r="E80">
-        <v>6.271199999999999</v>
+        <v>6.351599999999999</v>
       </c>
       <c r="F80">
-        <v>6.271199999999999</v>
+        <v>6.351599999999999</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7934,37 +7945,37 @@
         <v>-2.71</v>
       </c>
       <c r="M80">
-        <v>1.47874896</v>
+        <v>1.49770728</v>
       </c>
       <c r="N80">
-        <v>-4.18874896</v>
+        <v>-4.207707279999999</v>
       </c>
       <c r="O80">
-        <v>-1.04718724</v>
+        <v>-1.05192682</v>
       </c>
       <c r="P80">
-        <v>-3.14156172</v>
+        <v>-3.155780459999999</v>
       </c>
       <c r="Q80">
-        <v>2.53843828</v>
+        <v>2.52421954</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3889135177501926</v>
+        <v>0.4052522566906779</v>
       </c>
       <c r="T80">
-        <v>6.687921097806001</v>
+        <v>7.006393531034858</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.4581575496086908</v>
+        <v>-0.4523580869554162</v>
       </c>
       <c r="W80">
-        <v>0.3438335501977293</v>
+        <v>0.3424660369040872</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7972,7 +7983,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-1.832630198434764</v>
+        <v>-1.809432347821665</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7980,22 +7991,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3556511430592712</v>
+        <v>0.3575511430592712</v>
       </c>
       <c r="C81">
-        <v>-4.908596168360238</v>
+        <v>-4.997790706379284</v>
       </c>
       <c r="D81">
-        <v>1.443003831639762</v>
+        <v>1.434209293620716</v>
       </c>
       <c r="E81">
-        <v>6.351599999999999</v>
+        <v>6.431999999999999</v>
       </c>
       <c r="F81">
-        <v>6.351599999999999</v>
+        <v>6.431999999999999</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -8016,37 +8027,37 @@
         <v>-2.71</v>
       </c>
       <c r="M81">
-        <v>1.49770728</v>
+        <v>1.5166656</v>
       </c>
       <c r="N81">
-        <v>-4.207707279999999</v>
+        <v>-4.2266656</v>
       </c>
       <c r="O81">
-        <v>-1.05192682</v>
+        <v>-1.0566664</v>
       </c>
       <c r="P81">
-        <v>-3.155780459999999</v>
+        <v>-3.169999199999999</v>
       </c>
       <c r="Q81">
-        <v>2.52421954</v>
+        <v>2.5100008</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4052522566906779</v>
+        <v>0.4232248695252117</v>
       </c>
       <c r="T81">
-        <v>7.006393531034858</v>
+        <v>7.3567132075866</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.4523580869554162</v>
+        <v>-0.4467036108684735</v>
       </c>
       <c r="W81">
-        <v>0.3424660369040872</v>
+        <v>0.3411327114427861</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8054,7 +8065,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-1.809432347821665</v>
+        <v>-1.786814443473894</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8062,22 +8073,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3575511430592712</v>
+        <v>0.3594511430592712</v>
       </c>
       <c r="C82">
-        <v>-4.997790706379284</v>
+        <v>-5.086878695306408</v>
       </c>
       <c r="D82">
-        <v>1.434209293620716</v>
+        <v>1.425521304693591</v>
       </c>
       <c r="E82">
-        <v>6.431999999999999</v>
+        <v>6.5124</v>
       </c>
       <c r="F82">
-        <v>6.431999999999999</v>
+        <v>6.5124</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8098,37 +8109,37 @@
         <v>-2.71</v>
       </c>
       <c r="M82">
-        <v>1.5166656</v>
+        <v>1.53562392</v>
       </c>
       <c r="N82">
-        <v>-4.2266656</v>
+        <v>-4.24562392</v>
       </c>
       <c r="O82">
-        <v>-1.0566664</v>
+        <v>-1.06140598</v>
       </c>
       <c r="P82">
-        <v>-3.169999199999999</v>
+        <v>-3.18421794</v>
       </c>
       <c r="Q82">
-        <v>2.5100008</v>
+        <v>2.49578206</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4232248695252117</v>
+        <v>0.4430893363423282</v>
       </c>
       <c r="T82">
-        <v>7.3567132075866</v>
+        <v>7.743908639564842</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.4467036108684735</v>
+        <v>-0.4411887514750356</v>
       </c>
       <c r="W82">
-        <v>0.3411327114427861</v>
+        <v>0.3398323075978134</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8136,7 +8147,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-1.786814443473894</v>
+        <v>-1.764755005900143</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8144,22 +8155,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3594511430592712</v>
+        <v>0.3613511430592712</v>
       </c>
       <c r="C83">
-        <v>-5.086878695306408</v>
+        <v>-5.175862059805295</v>
       </c>
       <c r="D83">
-        <v>1.425521304693591</v>
+        <v>1.416937940194704</v>
       </c>
       <c r="E83">
-        <v>6.5124</v>
+        <v>6.5928</v>
       </c>
       <c r="F83">
-        <v>6.5124</v>
+        <v>6.5928</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8180,37 +8191,37 @@
         <v>-2.71</v>
       </c>
       <c r="M83">
-        <v>1.53562392</v>
+        <v>1.55458224</v>
       </c>
       <c r="N83">
-        <v>-4.24562392</v>
+        <v>-4.264582239999999</v>
       </c>
       <c r="O83">
-        <v>-1.06140598</v>
+        <v>-1.06614556</v>
       </c>
       <c r="P83">
-        <v>-3.18421794</v>
+        <v>-3.198436679999999</v>
       </c>
       <c r="Q83">
-        <v>2.49578206</v>
+        <v>2.48156332</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4430893363423282</v>
+        <v>0.4651609661391242</v>
       </c>
       <c r="T83">
-        <v>7.743908639564842</v>
+        <v>8.174125786207334</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.4411887514750356</v>
+        <v>-0.4358084008472912</v>
       </c>
       <c r="W83">
-        <v>0.3398323075978134</v>
+        <v>0.3385636209197913</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8218,7 +8229,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-1.764755005900143</v>
+        <v>-1.743233603389165</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8226,22 +8237,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3613511430592712</v>
+        <v>0.3632511430592712</v>
       </c>
       <c r="C84">
-        <v>-5.175862059805295</v>
+        <v>-5.264742678461841</v>
       </c>
       <c r="D84">
-        <v>1.416937940194704</v>
+        <v>1.408457321538159</v>
       </c>
       <c r="E84">
-        <v>6.5928</v>
+        <v>6.6732</v>
       </c>
       <c r="F84">
-        <v>6.5928</v>
+        <v>6.6732</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8262,37 +8273,37 @@
         <v>-2.71</v>
       </c>
       <c r="M84">
-        <v>1.55458224</v>
+        <v>1.57354056</v>
       </c>
       <c r="N84">
-        <v>-4.264582239999999</v>
+        <v>-4.28354056</v>
       </c>
       <c r="O84">
-        <v>-1.06614556</v>
+        <v>-1.07088514</v>
       </c>
       <c r="P84">
-        <v>-3.198436679999999</v>
+        <v>-3.21265542</v>
       </c>
       <c r="Q84">
-        <v>2.48156332</v>
+        <v>2.46734458</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4651609661391242</v>
+        <v>0.4898292582649551</v>
       </c>
       <c r="T84">
-        <v>8.174125786207334</v>
+        <v>8.654956714807767</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.4358084008472912</v>
+        <v>-0.4305576972226251</v>
       </c>
       <c r="W84">
-        <v>0.3385636209197913</v>
+        <v>0.337325505005095</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8300,7 +8311,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-1.743233603389165</v>
+        <v>-1.722230788890501</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8308,22 +8319,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3632511430592712</v>
+        <v>0.3651511430592712</v>
       </c>
       <c r="C85">
-        <v>-5.264742678461841</v>
+        <v>-5.353522385154876</v>
       </c>
       <c r="D85">
-        <v>1.408457321538159</v>
+        <v>1.400077614845124</v>
       </c>
       <c r="E85">
-        <v>6.6732</v>
+        <v>6.7536</v>
       </c>
       <c r="F85">
-        <v>6.6732</v>
+        <v>6.7536</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8344,37 +8355,37 @@
         <v>-2.71</v>
       </c>
       <c r="M85">
-        <v>1.57354056</v>
+        <v>1.59249888</v>
       </c>
       <c r="N85">
-        <v>-4.28354056</v>
+        <v>-4.30249888</v>
       </c>
       <c r="O85">
-        <v>-1.07088514</v>
+        <v>-1.07562472</v>
       </c>
       <c r="P85">
-        <v>-3.21265542</v>
+        <v>-3.22687416</v>
       </c>
       <c r="Q85">
-        <v>2.46734458</v>
+        <v>2.45312584</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4898292582649551</v>
+        <v>0.5175810869065148</v>
       </c>
       <c r="T85">
-        <v>8.654956714807767</v>
+        <v>9.195891509483253</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.4305576972226251</v>
+        <v>-0.4254320103509271</v>
       </c>
       <c r="W85">
-        <v>0.337325505005095</v>
+        <v>0.3361168680407486</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8382,7 +8393,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-1.722230788890501</v>
+        <v>-1.701728041403709</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8390,22 +8401,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3651511430592712</v>
+        <v>0.3670511430592712</v>
       </c>
       <c r="C86">
-        <v>-5.353522385154875</v>
+        <v>-5.44220297037824</v>
       </c>
       <c r="D86">
-        <v>1.400077614845124</v>
+        <v>1.391797029621758</v>
       </c>
       <c r="E86">
-        <v>6.753599999999999</v>
+        <v>6.833999999999999</v>
       </c>
       <c r="F86">
-        <v>6.753599999999999</v>
+        <v>6.833999999999999</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8426,37 +8437,37 @@
         <v>-2.71</v>
       </c>
       <c r="M86">
-        <v>1.59249888</v>
+        <v>1.6114572</v>
       </c>
       <c r="N86">
-        <v>-4.302498879999999</v>
+        <v>-4.321457199999999</v>
       </c>
       <c r="O86">
-        <v>-1.07562472</v>
+        <v>-1.0803643</v>
       </c>
       <c r="P86">
-        <v>-3.226874159999999</v>
+        <v>-3.241092899999999</v>
       </c>
       <c r="Q86">
-        <v>2.45312584</v>
+        <v>2.4389071</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5175810869065146</v>
+        <v>0.549033159366949</v>
       </c>
       <c r="T86">
-        <v>9.195891509483248</v>
+        <v>9.808950943448799</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.4254320103509272</v>
+        <v>-0.4204269278762104</v>
       </c>
       <c r="W86">
-        <v>0.3361168680407486</v>
+        <v>0.3349366695932104</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8464,7 +8475,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-1.701728041403709</v>
+        <v>-1.681707711504842</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8472,22 +8483,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3670511430592712</v>
+        <v>0.3689511430592712</v>
       </c>
       <c r="C87">
-        <v>-5.44220297037824</v>
+        <v>-5.53078618251621</v>
       </c>
       <c r="D87">
-        <v>1.391797029621758</v>
+        <v>1.383613817483789</v>
       </c>
       <c r="E87">
-        <v>6.833999999999999</v>
+        <v>6.914399999999999</v>
       </c>
       <c r="F87">
-        <v>6.833999999999999</v>
+        <v>6.914399999999999</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8508,37 +8519,37 @@
         <v>-2.71</v>
       </c>
       <c r="M87">
-        <v>1.6114572</v>
+        <v>1.63041552</v>
       </c>
       <c r="N87">
-        <v>-4.321457199999999</v>
+        <v>-4.340415519999999</v>
       </c>
       <c r="O87">
-        <v>-1.0803643</v>
+        <v>-1.08510388</v>
       </c>
       <c r="P87">
-        <v>-3.241092899999999</v>
+        <v>-3.255311639999999</v>
       </c>
       <c r="Q87">
-        <v>2.4389071</v>
+        <v>2.424688360000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.549033159366949</v>
+        <v>0.5849783850360166</v>
       </c>
       <c r="T87">
-        <v>9.808950943448799</v>
+        <v>10.50959029655228</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.4204269278762104</v>
+        <v>-0.4155382426683475</v>
       </c>
       <c r="W87">
-        <v>0.3349366695932104</v>
+        <v>0.3337839176211964</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8546,7 +8557,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-1.681707711504842</v>
+        <v>-1.66215297067339</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8554,22 +8565,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3689511430592712</v>
+        <v>0.3708511430592712</v>
       </c>
       <c r="C88">
-        <v>-5.53078618251621</v>
+        <v>-5.619273729074198</v>
       </c>
       <c r="D88">
-        <v>1.383613817483789</v>
+        <v>1.3755262709258</v>
       </c>
       <c r="E88">
-        <v>6.914399999999999</v>
+        <v>6.994799999999999</v>
       </c>
       <c r="F88">
-        <v>6.914399999999999</v>
+        <v>6.994799999999999</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8590,37 +8601,37 @@
         <v>-2.71</v>
       </c>
       <c r="M88">
-        <v>1.63041552</v>
+        <v>1.64937384</v>
       </c>
       <c r="N88">
-        <v>-4.340415519999999</v>
+        <v>-4.359373839999999</v>
       </c>
       <c r="O88">
-        <v>-1.08510388</v>
+        <v>-1.08984346</v>
       </c>
       <c r="P88">
-        <v>-3.255311639999999</v>
+        <v>-3.269530379999999</v>
       </c>
       <c r="Q88">
-        <v>2.424688360000001</v>
+        <v>2.410469620000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5849783850360166</v>
+        <v>0.6264536454234025</v>
       </c>
       <c r="T88">
-        <v>10.50959029655228</v>
+        <v>11.318020319364</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.4155382426683475</v>
+        <v>-0.4107619410284815</v>
       </c>
       <c r="W88">
-        <v>0.3337839176211964</v>
+        <v>0.3326576656945159</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8628,7 +8639,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-1.66215297067339</v>
+        <v>-1.643047764113926</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8636,22 +8647,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3708511430592712</v>
+        <v>0.3727511430592712</v>
       </c>
       <c r="C89">
-        <v>-5.619273729074198</v>
+        <v>-5.70766727786655</v>
       </c>
       <c r="D89">
-        <v>1.3755262709258</v>
+        <v>1.36753272213345</v>
       </c>
       <c r="E89">
-        <v>6.994799999999999</v>
+        <v>7.0752</v>
       </c>
       <c r="F89">
-        <v>6.994799999999999</v>
+        <v>7.0752</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8672,37 +8683,37 @@
         <v>-2.71</v>
       </c>
       <c r="M89">
-        <v>1.64937384</v>
+        <v>1.66833216</v>
       </c>
       <c r="N89">
-        <v>-4.359373839999999</v>
+        <v>-4.378332159999999</v>
       </c>
       <c r="O89">
-        <v>-1.08984346</v>
+        <v>-1.09458304</v>
       </c>
       <c r="P89">
-        <v>-3.269530379999999</v>
+        <v>-3.28374912</v>
       </c>
       <c r="Q89">
-        <v>2.410469620000001</v>
+        <v>2.39625088</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6264536454234025</v>
+        <v>0.6748414492086862</v>
       </c>
       <c r="T89">
-        <v>11.318020319364</v>
+        <v>12.261188679311</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.4107619410284815</v>
+        <v>-0.4060941916986123</v>
       </c>
       <c r="W89">
-        <v>0.3326576656945159</v>
+        <v>0.3315570104025328</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8710,7 +8721,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-1.643047764113926</v>
+        <v>-1.624376766794449</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8718,22 +8729,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3727511430592712</v>
+        <v>0.3746511430592712</v>
       </c>
       <c r="C90">
-        <v>-5.70766727786655</v>
+        <v>-5.795968458163148</v>
       </c>
       <c r="D90">
-        <v>1.36753272213345</v>
+        <v>1.359631541836852</v>
       </c>
       <c r="E90">
-        <v>7.0752</v>
+        <v>7.1556</v>
       </c>
       <c r="F90">
-        <v>7.0752</v>
+        <v>7.1556</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8754,37 +8765,37 @@
         <v>-2.71</v>
       </c>
       <c r="M90">
-        <v>1.66833216</v>
+        <v>1.68729048</v>
       </c>
       <c r="N90">
-        <v>-4.378332159999999</v>
+        <v>-4.39729048</v>
       </c>
       <c r="O90">
-        <v>-1.09458304</v>
+        <v>-1.09932262</v>
       </c>
       <c r="P90">
-        <v>-3.28374912</v>
+        <v>-3.29796786</v>
       </c>
       <c r="Q90">
-        <v>2.39625088</v>
+        <v>2.38203214</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6748414492086862</v>
+        <v>0.7320270355003848</v>
       </c>
       <c r="T90">
-        <v>12.261188679311</v>
+        <v>13.375842195612</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.4060941916986123</v>
+        <v>-0.401531335612111</v>
       </c>
       <c r="W90">
-        <v>0.3315570104025328</v>
+        <v>0.3304810889373358</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8792,7 +8803,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-1.624376766794449</v>
+        <v>-1.606125342448444</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8800,22 +8811,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3746511430592712</v>
+        <v>0.3765511430592712</v>
       </c>
       <c r="C91">
-        <v>-5.795968458163148</v>
+        <v>-5.884178861796514</v>
       </c>
       <c r="D91">
-        <v>1.359631541836852</v>
+        <v>1.351821138203486</v>
       </c>
       <c r="E91">
-        <v>7.1556</v>
+        <v>7.236</v>
       </c>
       <c r="F91">
-        <v>7.1556</v>
+        <v>7.236</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8836,37 +8847,37 @@
         <v>-2.71</v>
       </c>
       <c r="M91">
-        <v>1.68729048</v>
+        <v>1.7062488</v>
       </c>
       <c r="N91">
-        <v>-4.39729048</v>
+        <v>-4.4162488</v>
       </c>
       <c r="O91">
-        <v>-1.09932262</v>
+        <v>-1.1040622</v>
       </c>
       <c r="P91">
-        <v>-3.29796786</v>
+        <v>-3.3121866</v>
       </c>
       <c r="Q91">
-        <v>2.38203214</v>
+        <v>2.3678134</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7320270355003848</v>
+        <v>0.8006497390504235</v>
       </c>
       <c r="T91">
-        <v>13.375842195612</v>
+        <v>14.7134264151732</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.401531335612111</v>
+        <v>-0.397069876327532</v>
       </c>
       <c r="W91">
-        <v>0.3304810889373358</v>
+        <v>0.3294290768380321</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8874,7 +8885,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-1.606125342448444</v>
+        <v>-1.588279505310128</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8882,22 +8893,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3765511430592712</v>
+        <v>0.3784511430592712</v>
       </c>
       <c r="C92">
-        <v>-5.884178861796514</v>
+        <v>-5.972300044230956</v>
       </c>
       <c r="D92">
-        <v>1.351821138203486</v>
+        <v>1.344099955769043</v>
       </c>
       <c r="E92">
-        <v>7.236</v>
+        <v>7.3164</v>
       </c>
       <c r="F92">
-        <v>7.236</v>
+        <v>7.3164</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8918,37 +8929,37 @@
         <v>-2.71</v>
       </c>
       <c r="M92">
-        <v>1.7062488</v>
+        <v>1.72520712</v>
       </c>
       <c r="N92">
-        <v>-4.4162488</v>
+        <v>-4.435207119999999</v>
       </c>
       <c r="O92">
-        <v>-1.1040622</v>
+        <v>-1.10880178</v>
       </c>
       <c r="P92">
-        <v>-3.3121866</v>
+        <v>-3.32640534</v>
       </c>
       <c r="Q92">
-        <v>2.3678134</v>
+        <v>2.35359466</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8006497390504235</v>
+        <v>0.8845219322782485</v>
       </c>
       <c r="T92">
-        <v>14.7134264151732</v>
+        <v>16.34825157241467</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.397069876327532</v>
+        <v>-0.3927064710931635</v>
       </c>
       <c r="W92">
-        <v>0.3294290768380321</v>
+        <v>0.328400185883768</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8956,7 +8967,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-1.588279505310128</v>
+        <v>-1.570825884372654</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8964,22 +8975,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3784511430592712</v>
+        <v>0.3803511430592712</v>
       </c>
       <c r="C93">
-        <v>-5.972300044230956</v>
+        <v>-6.060333525595295</v>
       </c>
       <c r="D93">
-        <v>1.344099955769043</v>
+        <v>1.336466474404705</v>
       </c>
       <c r="E93">
-        <v>7.3164</v>
+        <v>7.3968</v>
       </c>
       <c r="F93">
-        <v>7.3164</v>
+        <v>7.3968</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -9000,37 +9011,37 @@
         <v>-2.71</v>
       </c>
       <c r="M93">
-        <v>1.72520712</v>
+        <v>1.74416544</v>
       </c>
       <c r="N93">
-        <v>-4.435207119999999</v>
+        <v>-4.45416544</v>
       </c>
       <c r="O93">
-        <v>-1.10880178</v>
+        <v>-1.11354136</v>
       </c>
       <c r="P93">
-        <v>-3.32640534</v>
+        <v>-3.34062408</v>
       </c>
       <c r="Q93">
-        <v>2.35359466</v>
+        <v>2.33937592</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8845219322782485</v>
+        <v>0.9893621738130297</v>
       </c>
       <c r="T93">
-        <v>16.34825157241467</v>
+        <v>18.39178301896651</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.3927064710931635</v>
+        <v>-0.3884379224943248</v>
       </c>
       <c r="W93">
-        <v>0.328400185883768</v>
+        <v>0.3273936621241618</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9038,7 +9049,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-1.570825884372654</v>
+        <v>-1.553751689977299</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9046,22 +9057,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3803511430592712</v>
+        <v>0.3822511430592712</v>
       </c>
       <c r="C94">
-        <v>-6.060333525595295</v>
+        <v>-6.148280791680587</v>
       </c>
       <c r="D94">
-        <v>1.336466474404705</v>
+        <v>1.328919208319413</v>
       </c>
       <c r="E94">
-        <v>7.3968</v>
+        <v>7.4772</v>
       </c>
       <c r="F94">
-        <v>7.3968</v>
+        <v>7.4772</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -9082,37 +9093,37 @@
         <v>-2.71</v>
       </c>
       <c r="M94">
-        <v>1.74416544</v>
+        <v>1.76312376</v>
       </c>
       <c r="N94">
-        <v>-4.45416544</v>
+        <v>-4.47312376</v>
       </c>
       <c r="O94">
-        <v>-1.11354136</v>
+        <v>-1.11828094</v>
       </c>
       <c r="P94">
-        <v>-3.34062408</v>
+        <v>-3.35484282</v>
       </c>
       <c r="Q94">
-        <v>2.33937592</v>
+        <v>2.32515718</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9893621738130297</v>
+        <v>1.124156770072034</v>
       </c>
       <c r="T94">
-        <v>18.39178301896651</v>
+        <v>21.01918059310458</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.3884379224943248</v>
+        <v>-0.3842611706395471</v>
       </c>
       <c r="W94">
-        <v>0.3273936621241618</v>
+        <v>0.3264087840368052</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9120,7 +9131,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-1.553751689977299</v>
+        <v>-1.537044682558188</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9128,22 +9139,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3822511430592712</v>
+        <v>0.3841511430592712</v>
       </c>
       <c r="C95">
-        <v>-6.148280791680587</v>
+        <v>-6.236143294904242</v>
       </c>
       <c r="D95">
-        <v>1.328919208319413</v>
+        <v>1.321456705095759</v>
       </c>
       <c r="E95">
-        <v>7.4772</v>
+        <v>7.5576</v>
       </c>
       <c r="F95">
-        <v>7.4772</v>
+        <v>7.5576</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9164,37 +9175,37 @@
         <v>-2.71</v>
       </c>
       <c r="M95">
-        <v>1.76312376</v>
+        <v>1.78208208</v>
       </c>
       <c r="N95">
-        <v>-4.47312376</v>
+        <v>-4.492082079999999</v>
       </c>
       <c r="O95">
-        <v>-1.11828094</v>
+        <v>-1.12302052</v>
       </c>
       <c r="P95">
-        <v>-3.35484282</v>
+        <v>-3.36906156</v>
       </c>
       <c r="Q95">
-        <v>2.32515718</v>
+        <v>2.31093844</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.124156770072034</v>
+        <v>1.303882898417374</v>
       </c>
       <c r="T95">
-        <v>21.01918059310458</v>
+        <v>24.52237735862202</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.3842611706395471</v>
+        <v>-0.3801732858455094</v>
       </c>
       <c r="W95">
-        <v>0.3264087840368052</v>
+        <v>0.3254448608023711</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9202,7 +9213,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-1.537044682558188</v>
+        <v>-1.520693143382037</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9210,22 +9221,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3841511430592712</v>
+        <v>0.3860511430592712</v>
       </c>
       <c r="C96">
-        <v>-6.236143294904242</v>
+        <v>-6.32392245524183</v>
       </c>
       <c r="D96">
-        <v>1.321456705095759</v>
+        <v>1.31407754475817</v>
       </c>
       <c r="E96">
-        <v>7.5576</v>
+        <v>7.638</v>
       </c>
       <c r="F96">
-        <v>7.5576</v>
+        <v>7.638</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9246,37 +9257,37 @@
         <v>-2.71</v>
       </c>
       <c r="M96">
-        <v>1.78208208</v>
+        <v>1.8010404</v>
       </c>
       <c r="N96">
-        <v>-4.492082079999999</v>
+        <v>-4.5110404</v>
       </c>
       <c r="O96">
-        <v>-1.12302052</v>
+        <v>-1.1277601</v>
       </c>
       <c r="P96">
-        <v>-3.36906156</v>
+        <v>-3.3832803</v>
       </c>
       <c r="Q96">
-        <v>2.31093844</v>
+        <v>2.2967197</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.303882898417374</v>
+        <v>1.555499478100849</v>
       </c>
       <c r="T96">
-        <v>24.52237735862202</v>
+        <v>29.42685283034644</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.3801732858455094</v>
+        <v>-0.3761714617839777</v>
       </c>
       <c r="W96">
-        <v>0.3254448608023711</v>
+        <v>0.324501230688662</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9284,7 +9295,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-1.520693143382037</v>
+        <v>-1.504685847135911</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9292,22 +9303,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3860511430592712</v>
+        <v>0.3879511430592713</v>
       </c>
       <c r="C97">
-        <v>-6.32392245524183</v>
+        <v>-6.411619661127849</v>
       </c>
       <c r="D97">
-        <v>1.31407754475817</v>
+        <v>1.306780338872151</v>
       </c>
       <c r="E97">
-        <v>7.638</v>
+        <v>7.7184</v>
       </c>
       <c r="F97">
-        <v>7.638</v>
+        <v>7.7184</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9328,37 +9339,37 @@
         <v>-2.71</v>
       </c>
       <c r="M97">
-        <v>1.8010404</v>
+        <v>1.81999872</v>
       </c>
       <c r="N97">
-        <v>-4.5110404</v>
+        <v>-4.52999872</v>
       </c>
       <c r="O97">
-        <v>-1.1277601</v>
+        <v>-1.13249968</v>
       </c>
       <c r="P97">
-        <v>-3.3832803</v>
+        <v>-3.39749904</v>
       </c>
       <c r="Q97">
-        <v>2.2967197</v>
+        <v>2.28250096</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.555499478100849</v>
+        <v>1.932924347626062</v>
       </c>
       <c r="T97">
-        <v>29.42685283034644</v>
+        <v>36.78356603793306</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.3761714617839777</v>
+        <v>-0.3722530090570612</v>
       </c>
       <c r="W97">
-        <v>0.324501230688662</v>
+        <v>0.3235772595356551</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9366,7 +9377,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-1.504685847135911</v>
+        <v>-1.489012036228245</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9374,22 +9385,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3879511430592712</v>
+        <v>0.3898511430592712</v>
       </c>
       <c r="C98">
-        <v>-6.411619661127848</v>
+        <v>-6.499236270326642</v>
       </c>
       <c r="D98">
-        <v>1.306780338872151</v>
+        <v>1.299563729673358</v>
       </c>
       <c r="E98">
-        <v>7.718399999999999</v>
+        <v>7.798799999999999</v>
       </c>
       <c r="F98">
-        <v>7.718399999999999</v>
+        <v>7.798799999999999</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9410,37 +9421,37 @@
         <v>-2.71</v>
       </c>
       <c r="M98">
-        <v>1.81999872</v>
+        <v>1.83895704</v>
       </c>
       <c r="N98">
-        <v>-4.529998719999999</v>
+        <v>-4.548957039999999</v>
       </c>
       <c r="O98">
-        <v>-1.13249968</v>
+        <v>-1.13723926</v>
       </c>
       <c r="P98">
-        <v>-3.39749904</v>
+        <v>-3.41171778</v>
       </c>
       <c r="Q98">
-        <v>2.28250096</v>
+        <v>2.26828222</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.932924347626057</v>
+        <v>2.561965796834742</v>
       </c>
       <c r="T98">
-        <v>36.78356603793296</v>
+        <v>49.04475471724395</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.3722530090570613</v>
+        <v>-0.3684153491698751</v>
       </c>
       <c r="W98">
-        <v>0.3235772595356551</v>
+        <v>0.3226723393342565</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9448,7 +9459,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-1.489012036228245</v>
+        <v>-1.4736613966795</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9456,22 +9467,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3898511430592712</v>
+        <v>0.3917511430592712</v>
       </c>
       <c r="C99">
-        <v>-6.499236270326642</v>
+        <v>-6.586773610774616</v>
       </c>
       <c r="D99">
-        <v>1.299563729673358</v>
+        <v>1.292426389225384</v>
       </c>
       <c r="E99">
-        <v>7.798799999999999</v>
+        <v>7.879199999999999</v>
       </c>
       <c r="F99">
-        <v>7.798799999999999</v>
+        <v>7.879199999999999</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9492,37 +9503,37 @@
         <v>-2.71</v>
       </c>
       <c r="M99">
-        <v>1.83895704</v>
+        <v>1.85791536</v>
       </c>
       <c r="N99">
-        <v>-4.548957039999999</v>
+        <v>-4.567915359999999</v>
       </c>
       <c r="O99">
-        <v>-1.13723926</v>
+        <v>-1.14197884</v>
       </c>
       <c r="P99">
-        <v>-3.41171778</v>
+        <v>-3.425936519999999</v>
       </c>
       <c r="Q99">
-        <v>2.26828222</v>
+        <v>2.254063480000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.561965796834742</v>
+        <v>3.820048695252114</v>
       </c>
       <c r="T99">
-        <v>49.04475471724395</v>
+        <v>73.56713207586593</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.3684153491698751</v>
+        <v>-0.3646560088722233</v>
       </c>
       <c r="W99">
-        <v>0.3226723393342565</v>
+        <v>0.3217858868920703</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9530,7 +9541,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-1.4736613966795</v>
+        <v>-1.458624035488893</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9538,22 +9549,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3917511430592712</v>
+        <v>0.3936511430592712</v>
       </c>
       <c r="C100">
-        <v>-6.586773610774616</v>
+        <v>-6.674232981394851</v>
       </c>
       <c r="D100">
-        <v>1.292426389225384</v>
+        <v>1.285367018605148</v>
       </c>
       <c r="E100">
-        <v>7.879199999999999</v>
+        <v>7.959599999999999</v>
       </c>
       <c r="F100">
-        <v>7.879199999999999</v>
+        <v>7.959599999999999</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9574,37 +9585,37 @@
         <v>-2.71</v>
       </c>
       <c r="M100">
-        <v>1.85791536</v>
+        <v>1.87687368</v>
       </c>
       <c r="N100">
-        <v>-4.567915359999999</v>
+        <v>-4.586873679999999</v>
       </c>
       <c r="O100">
-        <v>-1.14197884</v>
+        <v>-1.14671842</v>
       </c>
       <c r="P100">
-        <v>-3.425936519999999</v>
+        <v>-3.440155259999999</v>
       </c>
       <c r="Q100">
-        <v>2.254063480000001</v>
+        <v>2.239844740000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.820048695252114</v>
+        <v>7.594297390504227</v>
       </c>
       <c r="T100">
-        <v>73.56713207586593</v>
+        <v>147.1342641517319</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.3646560088722233</v>
+        <v>-0.3609726148432109</v>
       </c>
       <c r="W100">
-        <v>0.3217858868920703</v>
+        <v>0.3209173425800291</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9612,91 +9623,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-1.458624035488893</v>
+        <v>-1.443890459372843</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3936511430592712</v>
-      </c>
-      <c r="C101">
-        <v>-6.674232981394851</v>
-      </c>
-      <c r="D101">
-        <v>1.285367018605148</v>
-      </c>
-      <c r="E101">
-        <v>7.959599999999999</v>
-      </c>
-      <c r="F101">
-        <v>7.959599999999999</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.97</v>
-      </c>
-      <c r="K101">
-        <v>5.68</v>
-      </c>
-      <c r="L101">
-        <v>-2.71</v>
-      </c>
-      <c r="M101">
-        <v>1.87687368</v>
-      </c>
-      <c r="N101">
-        <v>-4.586873679999999</v>
-      </c>
-      <c r="O101">
-        <v>-1.14671842</v>
-      </c>
-      <c r="P101">
-        <v>-3.440155259999999</v>
-      </c>
-      <c r="Q101">
-        <v>2.239844740000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.594297390504227</v>
-      </c>
-      <c r="T101">
-        <v>147.1342641517319</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>-0.3609726148432109</v>
-      </c>
-      <c r="W101">
-        <v>0.3209173425800291</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-1.443890459372843</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
